--- a/src/attributions/attributions_saliency_traj_319.xlsx
+++ b/src/attributions/attributions_saliency_traj_319.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1606286019086838</v>
+        <v>1.654694514741095e-08</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6938199996948242</v>
+        <v>6.114918704724914e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07222764939069748</v>
+        <v>3.210021759514348e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>0.287342756986618</v>
+        <v>1.292885531967158e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2283751666545868</v>
+        <v>3.437485673885021e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1078704744577408</v>
+        <v>7.998370676887134e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2730573415756226</v>
+        <v>3.366702117091336e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0518977977335453</v>
+        <v>4.750501858552525e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1407979130744934</v>
+        <v>3.050491059752858e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003282390534877777</v>
+        <v>3.485758526267091e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6875560879707336</v>
+        <v>9.068347139873367e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06898575276136398</v>
+        <v>3.133943948796514e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3861314654350281</v>
+        <v>8.770880022268557e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1759847104549408</v>
+        <v>4.365787020788048e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1747831106185913</v>
+        <v>5.1364654751751e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1941075623035431</v>
+        <v>7.836113979919901e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06790187954902649</v>
+        <v>5.514983314469646e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1505609154701233</v>
+        <v>9.731378369792765e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1062624305486679</v>
+        <v>5.042200879046277e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1712701171636581</v>
+        <v>1.300221885713881e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06553640961647034</v>
+        <v>2.403196042166655e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04149370640516281</v>
+        <v>2.000535914703505e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1680967956781387</v>
+        <v>3.084620914250991e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006970373447984457</v>
+        <v>2.661360376521316e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00730479508638382</v>
+        <v>2.471688098637514e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1500530540943146</v>
+        <v>1.071471134039825e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07617392390966415</v>
+        <v>3.469605402983689e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04586213454604149</v>
+        <v>5.39028945922837e-08</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1274548172950745</v>
+        <v>4.081666560296071e-08</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0437689945101738</v>
+        <v>2.81738365970341e-09</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004465954378247261</v>
+        <v>2.568106793887637e-08</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.309493720531464e-05</v>
+        <v>2.968144663384464e-08</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1150730773806572</v>
+        <v>1.783851111269996e-08</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02153815142810345</v>
+        <v>1.028298068916911e-08</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.005147445946931839</v>
+        <v>1.14600844369761e-08</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.05836406350135803</v>
+        <v>1.20087317867501e-08</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1083048358559608</v>
+        <v>3.10464942643307e-09</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1014691591262817</v>
+        <v>4.910143402980793e-10</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.04690612107515335</v>
+        <v>1.416162298539803e-09</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.02092272415757179</v>
+        <v>4.280960919089694e-09</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.07379688322544098</v>
+        <v>1.262340187935251e-08</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.07209407538175583</v>
+        <v>7.412447544652423e-09</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.006709362845867872</v>
+        <v>3.381114410672126e-08</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0439312607049942</v>
+        <v>3.152013539065024e-09</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.04536258429288864</v>
+        <v>3.057121489291603e-08</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1836750358343124</v>
+        <v>1.23445600408445e-08</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.3713755309581757</v>
+        <v>8.208014179444945e-08</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.05774229764938354</v>
+        <v>1.989328168860993e-08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.05388013273477554</v>
+        <v>1.416002426424257e-09</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.05833179131150246</v>
+        <v>2.863636971994765e-08</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.217236265540123</v>
+        <v>1.022879025924794e-08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.213162362575531</v>
+        <v>1.752421097123147e-09</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.08224949240684509</v>
+        <v>4.572834555460759e-08</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1733575165271759</v>
+        <v>8.920546079593805e-09</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.07490241527557373</v>
+        <v>4.033027423133717e-08</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.05792342126369476</v>
+        <v>2.369636931121022e-08</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1408943235874176</v>
+        <v>1.457410014893412e-08</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2200398743152618</v>
+        <v>2.799103171469142e-10</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.418897420167923</v>
+        <v>3.381833124649347e-08</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.01701401360332966</v>
+        <v>5.116979906460983e-08</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.02819006145000458</v>
+        <v>1.355718826090424e-08</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.05843498185276985</v>
+        <v>1.394051007963526e-08</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.03655417263507843</v>
+        <v>6.984681988342345e-08</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.04240136221051216</v>
+        <v>2.879132843247589e-08</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1433822512626648</v>
+        <v>9.151388979944386e-09</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.03573763370513916</v>
+        <v>9.754720586840904e-09</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.03293881192803383</v>
+        <v>1.269975324902362e-08</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0717218816280365</v>
+        <v>1.737543997570867e-09</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.07383237779140472</v>
+        <v>3.359609834774346e-08</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1344357430934906</v>
+        <v>6.272246277916338e-09</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.01355081982910633</v>
+        <v>5.492973187415373e-09</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.001630197279155254</v>
+        <v>5.673503444825201e-09</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.06017193198204041</v>
+        <v>2.074556171294262e-08</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1910675913095474</v>
+        <v>2.354979500296395e-08</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.09069357067346573</v>
+        <v>2.592670966805599e-08</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.01359742879867554</v>
+        <v>2.582359570624249e-08</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1719447076320648</v>
+        <v>2.655188291456057e-09</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1637243926525116</v>
+        <v>5.354745624686075e-08</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1116794496774673</v>
+        <v>2.388594566582469e-08</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.03898602724075317</v>
+        <v>1.947003624991339e-08</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1107047274708748</v>
+        <v>5.596980656719097e-09</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.03352706879377365</v>
+        <v>8.492720304786872e-09</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1590429991483688</v>
+        <v>6.090505433320459e-09</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.08521562069654465</v>
+        <v>3.584070817908014e-09</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.01021840795874596</v>
+        <v>1.358879764268295e-08</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01227798033505678</v>
+        <v>1.301213181648109e-08</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.05222462117671967</v>
+        <v>2.051319647478067e-08</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.07224896550178528</v>
+        <v>4.310347634373102e-09</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.02150659635663033</v>
+        <v>8.864004641395695e-09</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.03059499524533749</v>
+        <v>6.889715020719223e-09</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.138804629445076</v>
+        <v>2.487246497651086e-08</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.001369731035083532</v>
+        <v>1.000800242678679e-08</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.01669886708259583</v>
+        <v>2.202092508341025e-09</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1908066421747208</v>
+        <v>1.932102478008346e-08</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.08058178424835205</v>
+        <v>8.276952456753861e-10</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.04780180752277374</v>
+        <v>3.579442875434324e-08</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.04437122121453285</v>
+        <v>5.969518657167328e-09</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.07581364363431931</v>
+        <v>5.198492658564646e-08</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.02485701628029346</v>
+        <v>3.031586004453857e-08</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.02482687868177891</v>
+        <v>8.269973150731857e-09</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1718378514051437</v>
+        <v>1.544218264371011e-08</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.09196379035711288</v>
+        <v>2.032325419065728e-09</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.05544444918632507</v>
+        <v>1.58203903311005e-08</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01119169406592846</v>
+        <v>1.097660096149866e-08</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0613076239824295</v>
+        <v>1.46652743282516e-08</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0875638946890831</v>
+        <v>2.965944378985341e-09</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.03650360554456711</v>
+        <v>3.395149938967279e-09</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.008046960458159447</v>
+        <v>7.817808622689881e-09</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1854655295610428</v>
+        <v>6.832013177415774e-09</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.03327707201242447</v>
+        <v>4.232490802280608e-09</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1119286492466927</v>
+        <v>6.454576606529372e-08</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.07723401486873627</v>
+        <v>2.741265703321005e-08</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.07978211343288422</v>
+        <v>1.646877301197947e-08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.00722910463809967</v>
+        <v>1.313498643185085e-08</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.04199895262718201</v>
+        <v>3.239683010747285e-08</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.05926354601979256</v>
+        <v>5.803001634774319e-09</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.03513465821743011</v>
+        <v>1.657396708765191e-08</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.109746590256691</v>
+        <v>4.104365736168347e-09</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.06694334000349045</v>
+        <v>1.099568436302434e-08</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.05681882426142693</v>
+        <v>1.180484598961584e-09</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.08748696744441986</v>
+        <v>4.223576510753446e-08</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0384877510368824</v>
+        <v>2.158312462086087e-08</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.01528134290128946</v>
+        <v>1.20354712862536e-08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07594403624534607</v>
+        <v>3.879124932382183e-08</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.0137941911816597</v>
+        <v>1.872266608415885e-08</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.07198334485292435</v>
+        <v>1.606825428268621e-08</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.04062489792704582</v>
+        <v>1.917834779874283e-08</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1562781482934952</v>
+        <v>3.546823634792418e-08</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.1630293279886246</v>
+        <v>4.051567970009273e-09</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0715070366859436</v>
+        <v>4.89448481744148e-10</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1006272211670876</v>
+        <v>7.22218951310083e-09</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.04875502362847328</v>
+        <v>2.955026623396861e-08</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01882528699934483</v>
+        <v>4.957940547001272e-08</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.04323166608810425</v>
+        <v>3.440091322914895e-09</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.07595545053482056</v>
+        <v>3.210073984405426e-08</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.01078712940216064</v>
+        <v>5.686600523802099e-09</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1064713373780251</v>
+        <v>4.169874401327434e-08</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.06331668049097061</v>
+        <v>2.53495735513809e-09</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.05159600079059601</v>
+        <v>1.042301356335429e-08</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.04374856501817703</v>
+        <v>2.695017720100168e-08</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.07596646994352341</v>
+        <v>4.481036652848047e-10</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.1037807613611221</v>
+        <v>9.754232976888488e-09</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.04517116397619247</v>
+        <v>2.530704978909171e-09</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.01349648460745811</v>
+        <v>1.607570432327066e-08</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.05310402438044548</v>
+        <v>2.879342542172481e-09</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.06287923455238342</v>
+        <v>9.157206548593422e-09</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.1207446753978729</v>
+        <v>3.358819711252181e-08</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.05867713317275047</v>
+        <v>5.546914483289811e-09</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.0171851571649313</v>
+        <v>7.396695256289831e-09</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01588659174740314</v>
+        <v>1.334940158415066e-08</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.05428929999470711</v>
+        <v>3.447472707307497e-08</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.1047749221324921</v>
+        <v>1.8074857166539e-08</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.05681165680289268</v>
+        <v>1.719516751208516e-09</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.04215310141444206</v>
+        <v>1.351627076928708e-08</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1541485786437988</v>
+        <v>9.478280382779758e-09</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.08125770092010498</v>
+        <v>5.689851700907411e-09</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01396344136446714</v>
+        <v>1.436514196484495e-08</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0274763572961092</v>
+        <v>1.983449138265314e-08</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.06845374405384064</v>
+        <v>1.189561515957394e-08</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.09710867702960968</v>
+        <v>4.383064133861581e-09</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.0112165305763483</v>
+        <v>2.579105595756914e-09</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.03218277171254158</v>
+        <v>6.606386104834883e-09</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.04352403432130814</v>
+        <v>3.798083270112329e-08</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.03403247892856598</v>
+        <v>6.518704509517192e-08</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.1579293608665466</v>
+        <v>1.218260514690428e-08</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.04969272390007973</v>
+        <v>1.423608964046252e-08</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.09554170817136765</v>
+        <v>3.915815227628627e-09</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.04500973969697952</v>
+        <v>3.605878706736121e-09</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.00309463869780302</v>
+        <v>1.743540956056222e-08</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.04408887028694153</v>
+        <v>1.890245293623138e-08</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.08869393914937973</v>
+        <v>4.909168183075963e-08</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1906469762325287</v>
+        <v>6.017341291908451e-09</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2604555189609528</v>
+        <v>1.062412451346972e-07</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.1107891201972961</v>
+        <v>1.411944250406805e-08</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.05512213706970215</v>
+        <v>5.044595852154998e-09</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01748219132423401</v>
+        <v>4.572997269747248e-08</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.01049568876624107</v>
+        <v>6.750401837507525e-08</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.02384681440889835</v>
+        <v>6.44107629454993e-08</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.04889760911464691</v>
+        <v>6.924527440332895e-08</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.02370122447609901</v>
+        <v>1.256179604780527e-09</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.1411280930042267</v>
+        <v>1.048194953057191e-08</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.002311610151082277</v>
+        <v>1.231797686074287e-08</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.0813019797205925</v>
+        <v>8.339826607084433e-09</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.02398736402392387</v>
+        <v>1.882306932543543e-08</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.1623586565256119</v>
+        <v>7.803462320765675e-10</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.05038933828473091</v>
+        <v>1.805826777001585e-08</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.1752824932336807</v>
+        <v>2.241353769250054e-08</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.05386041849851608</v>
+        <v>1.061660181989055e-08</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.03587028011679649</v>
+        <v>8.920686411784118e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2706,3985 +2706,3985 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.3553149104118347</v>
+        <v>0.0008803904056549072</v>
       </c>
       <c r="B5" t="n">
-        <v>2.858385324478149</v>
+        <v>1.636051058769226</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2103201448917389</v>
+        <v>0.3994303643703461</v>
       </c>
       <c r="D5" t="n">
-        <v>2.158892393112183</v>
+        <v>1.073657274246216</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8795714378356934</v>
+        <v>0.1205921173095703</v>
       </c>
       <c r="F5" t="n">
-        <v>1.127333521842957</v>
+        <v>0.5865910053253174</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06015628576278687</v>
+        <v>0.5475225448608398</v>
       </c>
       <c r="H5" t="n">
-        <v>0.13018599152565</v>
+        <v>0.2483409941196442</v>
       </c>
       <c r="I5" t="n">
-        <v>1.284874081611633</v>
+        <v>0.2979366481304169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7520114183425903</v>
+        <v>0.1609794497489929</v>
       </c>
       <c r="K5" t="n">
-        <v>2.182872533798218</v>
+        <v>1.717676520347595</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0816292017698288</v>
+        <v>0.425553947687149</v>
       </c>
       <c r="M5" t="n">
-        <v>2.22637152671814</v>
+        <v>1.566056609153748</v>
       </c>
       <c r="N5" t="n">
-        <v>0.395275741815567</v>
+        <v>0.02855892851948738</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5136810541152954</v>
+        <v>0.2464689463376999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3692291975021362</v>
+        <v>0.2291372865438461</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6759278178215027</v>
+        <v>0.6180235743522644</v>
       </c>
       <c r="R5" t="n">
-        <v>1.065195202827454</v>
+        <v>0.1865856945514679</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2831949293613434</v>
+        <v>0.03370759263634682</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4243837594985962</v>
+        <v>0.3773056864738464</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3088666200637817</v>
+        <v>0.4379693567752838</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1387649476528168</v>
+        <v>0.06292115896940231</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1478410214185715</v>
+        <v>0.02375799417495728</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1731500327587128</v>
+        <v>0.3839540779590607</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3177500069141388</v>
+        <v>0.08268206566572189</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2196594327688217</v>
+        <v>0.1358142048120499</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2204426825046539</v>
+        <v>0.2689028978347778</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2232390940189362</v>
+        <v>0.1426933109760284</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5226624011993408</v>
+        <v>0.464825302362442</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2393239289522171</v>
+        <v>0.0466473251581192</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.06763401627540588</v>
+        <v>0.7708172798156738</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02735049277544022</v>
+        <v>0.0174311026930809</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.04203444719314575</v>
+        <v>0.4234397113323212</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.06045866757631302</v>
+        <v>0.1280145198106766</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1220410466194153</v>
+        <v>0.2480311542749405</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.06359772384166718</v>
+        <v>0.1320820450782776</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.3392206728458405</v>
+        <v>0.01042176224291325</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5424767732620239</v>
+        <v>0.4982393383979797</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.2238019704818726</v>
+        <v>0.3301389217376709</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.04876896366477013</v>
+        <v>0.1808053255081177</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0232490636408329</v>
+        <v>0.3996839225292206</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.2860974371433258</v>
+        <v>0.1627460569143295</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.2327007800340652</v>
+        <v>0.1590558737516403</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.3328603804111481</v>
+        <v>0.2003258317708969</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1417703032493591</v>
+        <v>0.08351150155067444</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1661567538976669</v>
+        <v>0.08200391381978989</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.89475953578949</v>
+        <v>0.96893310546875</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2278187274932861</v>
+        <v>0.127098873257637</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.8797698020935059</v>
+        <v>0.7200260162353516</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.4271530508995056</v>
+        <v>0.1687260121107101</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.8243422508239746</v>
+        <v>0.26751908659935</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.7573975324630737</v>
+        <v>0.1351440697908401</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.5469759106636047</v>
+        <v>0.3014843761920929</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.5313131809234619</v>
+        <v>0.03530990332365036</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.2425217926502228</v>
+        <v>0.1250573247671127</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1262966692447662</v>
+        <v>0.1892697513103485</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.2818993628025055</v>
+        <v>0.1774270385503769</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4127268493175507</v>
+        <v>0.1166650205850601</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.038666486740112</v>
+        <v>0.1168425679206848</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.3274601697921753</v>
+        <v>0.5845606923103333</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.5511887669563293</v>
+        <v>0.2792569994926453</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4386327564716339</v>
+        <v>0.2622541487216949</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.150391340255737</v>
+        <v>0.629077672958374</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.09094393253326416</v>
+        <v>0.06161415576934814</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.4608298540115356</v>
+        <v>0.4402950704097748</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.1434398293495178</v>
+        <v>0.05485062673687935</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.2521853446960449</v>
+        <v>0.007232218980789185</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.3275383114814758</v>
+        <v>0.159980908036232</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.08529654145240784</v>
+        <v>0.06051131337881088</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.5041049718856812</v>
+        <v>0.1048510372638702</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.368433028459549</v>
+        <v>0.1333194077014923</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.02107026986777782</v>
+        <v>0.0945575013756752</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.2801420390605927</v>
+        <v>0.01423746347427368</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.978045642375946</v>
+        <v>0.7486693263053894</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.5858242511749268</v>
+        <v>0.1836092174053192</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.7863037586212158</v>
+        <v>0.3883994519710541</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.09767308086156845</v>
+        <v>0.08058101683855057</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.3548663854598999</v>
+        <v>0.319734513759613</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.2363225221633911</v>
+        <v>0.1398244202136993</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.09908829629421234</v>
+        <v>0.3742338716983795</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.1704294681549072</v>
+        <v>0.2500669658184052</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.05222667008638382</v>
+        <v>0.03969623148441315</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.4015092253684998</v>
+        <v>0.439666211605072</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.2584038376808167</v>
+        <v>0.2440938353538513</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1990093886852264</v>
+        <v>0.3775106072425842</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.08759498596191406</v>
+        <v>0.02145177498459816</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1388600915670395</v>
+        <v>0.04922971874475479</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1392607092857361</v>
+        <v>0.0955566018819809</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.1648204773664474</v>
+        <v>0.1231762692332268</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.1439243257045746</v>
+        <v>0.07228703051805496</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.536513090133667</v>
+        <v>0.07160727679729462</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.3769981265068054</v>
+        <v>0.05369117110967636</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1260693073272705</v>
+        <v>0.1279129385948181</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.2095221430063248</v>
+        <v>0.793788731098175</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.00699220597743988</v>
+        <v>0.3029015064239502</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.6308104395866394</v>
+        <v>0.1174222826957703</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.6033110022544861</v>
+        <v>0.1328939199447632</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.3593356013298035</v>
+        <v>0.1512535512447357</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1635283380746841</v>
+        <v>0.406932145357132</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.04662294685840607</v>
+        <v>0.04907915368676186</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.4358567893505096</v>
+        <v>0.4696364402770996</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.2291887998580933</v>
+        <v>0.2649087309837341</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.3021743595600128</v>
+        <v>0.4233755171298981</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0720246359705925</v>
+        <v>0.01486051920801401</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.1530657410621643</v>
+        <v>0.004601814784109592</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.1848189532756805</v>
+        <v>0.09095366299152374</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.1785477995872498</v>
+        <v>0.1562156677246094</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.06678807735443115</v>
+        <v>0.06673377752304077</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.4789478182792664</v>
+        <v>0.1229622364044189</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.5539076924324036</v>
+        <v>0.679146409034729</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.007028877735137939</v>
+        <v>0.5287885665893555</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01887780427932739</v>
+        <v>0.3468341827392578</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.5369224548339844</v>
+        <v>0.1272399425506592</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.2159271389245987</v>
+        <v>0.6390884518623352</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.5154972076416016</v>
+        <v>0.1132241860032082</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4224684238433838</v>
+        <v>0.7381380796432495</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.04179885983467102</v>
+        <v>0.04185225069522858</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.1205146908760071</v>
+        <v>0.04958979040384293</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.006650004535913467</v>
+        <v>0.01853006705641747</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.09676021337509155</v>
+        <v>0.1273834407329559</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.1994928419589996</v>
+        <v>0.07355773448944092</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.051165372133255</v>
+        <v>0.05155842006206512</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.5452939867973328</v>
+        <v>0.1917424499988556</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.05788353458046913</v>
+        <v>0.2011715471744537</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.08519844710826874</v>
+        <v>0.07176847010850906</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.2545540034770966</v>
+        <v>0.6286101341247559</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.887232065200806e-05</v>
+        <v>0.09164844453334808</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.3025075197219849</v>
+        <v>0.2020704448223114</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.3031393587589264</v>
+        <v>0.3048295080661774</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.3523921966552734</v>
+        <v>0.1030570268630981</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.3776037395000458</v>
+        <v>0.1252050995826721</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.1770527362823486</v>
+        <v>0.05240423977375031</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.02252480015158653</v>
+        <v>0.1360659003257751</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.06176234781742096</v>
+        <v>0.4204754233360291</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.2588774561882019</v>
+        <v>0.2908021509647369</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.09661012142896652</v>
+        <v>0.1194979324936867</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.364232063293457</v>
+        <v>0.4192650616168976</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.3097751140594482</v>
+        <v>0.09512579441070557</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.04681389406323433</v>
+        <v>0.3845489919185638</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.2004545331001282</v>
+        <v>0.01701209507882595</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.3874640762805939</v>
+        <v>0.251875251531601</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.2521849274635315</v>
+        <v>0.05316123366355896</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0294300876557827</v>
+        <v>0.1337090134620667</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0277034230530262</v>
+        <v>0.01029402390122414</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.06505055725574493</v>
+        <v>0.1625553816556931</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.4302908480167389</v>
+        <v>0.2612157464027405</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.3597306907176971</v>
+        <v>0.01909051090478897</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.4828251600265503</v>
+        <v>0.3317853212356567</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.1770029067993164</v>
+        <v>0.001963537419214845</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.8396661877632141</v>
+        <v>0.1247537434101105</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.5465872287750244</v>
+        <v>0.1818948239088058</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.2536597549915314</v>
+        <v>0.07795989513397217</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.1573994159698486</v>
+        <v>0.4029246270656586</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.088394895195961</v>
+        <v>0.04515056312084198</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.4752965867519379</v>
+        <v>0.4344534277915955</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.1245594918727875</v>
+        <v>0.2047590166330338</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.318747490644455</v>
+        <v>0.4457685351371765</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.2224450409412384</v>
+        <v>0.05041613429784775</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.2022271454334259</v>
+        <v>0.021063182502985</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.2528613805770874</v>
+        <v>0.07736866176128387</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.1686806082725525</v>
+        <v>0.1393314301967621</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.1342756897211075</v>
+        <v>0.05854042246937752</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.09934923052787781</v>
+        <v>0.04376023262739182</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.2331806719303131</v>
+        <v>0.3878145515918732</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.1962933093309402</v>
+        <v>0.1391890347003937</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.4690245985984802</v>
+        <v>0.3313326239585876</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.3106458783149719</v>
+        <v>0.225897490978241</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.3754733800888062</v>
+        <v>0.1964510381221771</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.3812968134880066</v>
+        <v>0.09071462601423264</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2483242452144623</v>
+        <v>0.122371681034565</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.2591101229190826</v>
+        <v>0.3998567461967468</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.3077524900436401</v>
+        <v>0.26639723777771</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.4743227362632751</v>
+        <v>0.7917993068695068</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.1127013340592384</v>
+        <v>0.5972006320953369</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.7153181433677673</v>
+        <v>0.3775901794433594</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.5766192674636841</v>
+        <v>0.3506681621074677</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.3563375771045685</v>
+        <v>0.4833399057388306</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.3866485953330994</v>
+        <v>0.07203701883554459</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.1414591372013092</v>
+        <v>0.06194735690951347</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.122144341468811</v>
+        <v>0.2256155014038086</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.404483288526535</v>
+        <v>0.4659404456615448</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.1091585457324982</v>
+        <v>0.6514603495597839</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.06839724630117416</v>
+        <v>0.5869972705841064</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.08792991936206818</v>
+        <v>0.2876259088516235</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.4814445972442627</v>
+        <v>0.2707653045654297</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.005279656499624252</v>
+        <v>0.06763549894094467</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.5420293807983398</v>
+        <v>0.388559877872467</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.2024208754301071</v>
+        <v>0.1214157268404961</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.04740797355771065</v>
+        <v>0.002668047323822975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.008663078770041466</v>
+        <v>0.006338121835142374</v>
       </c>
       <c r="B6" t="n">
-        <v>0.910790741443634</v>
+        <v>0.02070117741823196</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02939340099692345</v>
+        <v>0.001828969223424792</v>
       </c>
       <c r="D6" t="n">
-        <v>0.76458740234375</v>
+        <v>0.01528878696262836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1899759024381638</v>
+        <v>0.001597157446667552</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1802384257316589</v>
+        <v>0.006440496072173119</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001660965383052826</v>
+        <v>0.006405090447515249</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1872439533472061</v>
+        <v>0.004142773803323507</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05458369106054306</v>
+        <v>4.366540815681219e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07034467160701752</v>
+        <v>0.00995337963104248</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7556458711624146</v>
+        <v>0.01854794099926949</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01554829627275467</v>
+        <v>0.004287784919142723</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6182705760002136</v>
+        <v>0.02425364963710308</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2984151542186737</v>
+        <v>0.001400702865794301</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2207180112600327</v>
+        <v>0.005213790573179722</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03011768311262131</v>
+        <v>0.006324360147118568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06112314015626907</v>
+        <v>0.001416259910911322</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1326952278614044</v>
+        <v>0.001305407844483852</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05250271409749985</v>
+        <v>0.001939360518008471</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1342156827449799</v>
+        <v>0.006141786463558674</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01130126416683197</v>
+        <v>0.001176811289042234</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03709116205573082</v>
+        <v>0.001452938304282725</v>
       </c>
       <c r="W6" t="n">
-        <v>0.080330491065979</v>
+        <v>0.003396402578800917</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1476623862981796</v>
+        <v>0.001951618818566203</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1510376036167145</v>
+        <v>0.001410171738825738</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0612984336912632</v>
+        <v>0.003259444609284401</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.06392938643693924</v>
+        <v>0.00091145234182477</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1214239969849586</v>
+        <v>0.0004085380351170897</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07197855412960052</v>
+        <v>0.002044387627393007</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01482109166681767</v>
+        <v>0.0005418447544798255</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.02737404964864254</v>
+        <v>0.0005364635726436973</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1974218040704727</v>
+        <v>0.0009601647034287453</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1051854193210602</v>
+        <v>0.0011276809964329</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.08521772921085358</v>
+        <v>9.074481204152107e-05</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.006194110028445721</v>
+        <v>0.0001179415266960859</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01998127624392509</v>
+        <v>0.0007601329125463963</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.01747567020356655</v>
+        <v>0.0005414555780589581</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1321744173765182</v>
+        <v>0.005998061038553715</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.02910290472209454</v>
+        <v>0.0007617846131324768</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.008676023222506046</v>
+        <v>0.0008947511669248343</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.1203553304076195</v>
+        <v>0.006301323883235455</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.08965736627578735</v>
+        <v>0.003350151935592294</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.07775804400444031</v>
+        <v>0.002800329588353634</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.04477891698479652</v>
+        <v>0.001441759988665581</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1109806671738625</v>
+        <v>0.0004601067630574107</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1100393086671829</v>
+        <v>0.002386985346674919</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.5020191669464111</v>
+        <v>0.01021051965653896</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.01744683645665646</v>
+        <v>0.002940831705927849</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.3673062324523926</v>
+        <v>0.008050113916397095</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01706671714782715</v>
+        <v>0.004634718410670757</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0726197212934494</v>
+        <v>0.001035297405906022</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2340419888496399</v>
+        <v>0.000225619412958622</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1792931705713272</v>
+        <v>0.003078812500461936</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.02583087608218193</v>
+        <v>0.004191138781607151</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.005028963088989258</v>
+        <v>0.003325895871967077</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.2171849757432938</v>
+        <v>0.001005727332085371</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1394061148166656</v>
+        <v>0.003879449795931578</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.06460294872522354</v>
+        <v>0.0007796842255629599</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1340822875499725</v>
+        <v>0.0001514072064310312</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0657486766576767</v>
+        <v>0.002959481673315167</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1567476987838745</v>
+        <v>0.004582389257848263</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.06422349810600281</v>
+        <v>0.001303027733229101</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.1768297106027603</v>
+        <v>0.00398609833791852</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.08971209824085236</v>
+        <v>0.004460792988538742</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.09397789835929871</v>
+        <v>0.005482194479554892</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.009958667680621147</v>
+        <v>9.181430505122989e-05</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0668988823890686</v>
+        <v>0.001511681242845953</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1154203936457634</v>
+        <v>0.002833793871104717</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.06865203380584717</v>
+        <v>0.001298727700486779</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.05789797753095627</v>
+        <v>0.0003109385725110769</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01233375258743763</v>
+        <v>0.001059541711583734</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.07814686745405197</v>
+        <v>0.0008514914661645889</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1018843948841095</v>
+        <v>1.102191163226962e-05</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2804169952869415</v>
+        <v>0.009787406772375107</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.04513835534453392</v>
+        <v>7.808231748640537e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.2091387808322906</v>
+        <v>0.006777189671993256</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.04094932228326797</v>
+        <v>0.003219965845346451</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.02115469798445702</v>
+        <v>0.001968996366485953</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.06981845945119858</v>
+        <v>0.0005747814429923892</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1372070461511612</v>
+        <v>0.002917193342000246</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.1228302866220474</v>
+        <v>0.0008716071024537086</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.02194386720657349</v>
+        <v>0.002459555864334106</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.115187369287014</v>
+        <v>0.005004890263080597</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.04381249099969864</v>
+        <v>0.000435672583989799</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1449876725673676</v>
+        <v>0.005071669816970825</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.01355624385178089</v>
+        <v>0.002265474759042263</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0100567638874054</v>
+        <v>0.0004289587086532265</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.04268999397754669</v>
+        <v>0.0003843353770207614</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.01845330744981766</v>
+        <v>0.0006323951529338956</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.007235732860863209</v>
+        <v>0.0001760515733622015</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1502868384122849</v>
+        <v>0.001510618953034282</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.02536566741764545</v>
+        <v>0.001749934279359877</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.04758237302303314</v>
+        <v>0.001976892817765474</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1002828553318977</v>
+        <v>0.008866848424077034</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1245464906096458</v>
+        <v>0.0008998664561659098</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.04747835546731949</v>
+        <v>0.001418480300344527</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1526366919279099</v>
+        <v>0.0005053153145126998</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.3027733266353607</v>
+        <v>0.003329433035105467</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.09808684140443802</v>
+        <v>0.0001097491476684809</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.01192562654614449</v>
+        <v>0.002913882723078132</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.1415901780128479</v>
+        <v>0.005889941472560167</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.06278576701879501</v>
+        <v>0.0002800725633278489</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.14922696352005</v>
+        <v>0.004643938504159451</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01023944467306137</v>
+        <v>0.001468914793804288</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.03966636955738068</v>
+        <v>0.0001943420502357185</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.05359842628240585</v>
+        <v>0.0003167674585711211</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.02158838510513306</v>
+        <v>0.00031041688635014</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.03356961533427238</v>
+        <v>0.0009083867771551013</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.01364374253898859</v>
+        <v>0.003902659751474857</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.2529838383197784</v>
+        <v>0.008637620136141777</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.01281046122312546</v>
+        <v>0.007180101703852415</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.3944578170776367</v>
+        <v>0.006258734501898289</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.03291678428649902</v>
+        <v>0.002551362151280046</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.05249920859932899</v>
+        <v>0.01100018713623285</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.1406986713409424</v>
+        <v>0.0008284147479571402</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0893738865852356</v>
+        <v>0.005063909571617842</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.008273886516690254</v>
+        <v>0.001142490305937827</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.02517251297831535</v>
+        <v>0.0008888535085134208</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.09091382473707199</v>
+        <v>0.004465693607926369</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.09166599810123444</v>
+        <v>1.600931864231825e-05</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.02215765602886677</v>
+        <v>0.003576389979571104</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.04415808618068695</v>
+        <v>0.00192078307736665</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05513661727309227</v>
+        <v>0.0001183690037578344</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.03682132810354233</v>
+        <v>0.0001887647667899728</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.04569819569587708</v>
+        <v>0.002280620858073235</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.06964575499296188</v>
+        <v>0.005326726473867893</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0088693518191576</v>
+        <v>0.0004299268184695393</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.05460076406598091</v>
+        <v>0.0005389440921135247</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.07275280356407166</v>
+        <v>0.0008909314638003707</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.03935049846768379</v>
+        <v>0.005471426527947187</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.02967380173504353</v>
+        <v>0.004793347790837288</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.09409406781196594</v>
+        <v>0.007664062082767487</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.05977308005094528</v>
+        <v>0.001232703914865851</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.04878914728760719</v>
+        <v>0.007508993148803711</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.01326293312013149</v>
+        <v>0.004914402030408382</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.03638268634676933</v>
+        <v>0.006482964381575584</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.1210415363311768</v>
+        <v>0.00367084564641118</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0552649199962616</v>
+        <v>0.000941261590924114</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.2909530401229858</v>
+        <v>0.005793766584247351</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.07111880928277969</v>
+        <v>0.0009818939724937081</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.05391699820756912</v>
+        <v>0.002247876720502973</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.05301816761493683</v>
+        <v>0.0001306963094975799</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.03140764310956001</v>
+        <v>0.0001901521027320996</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.02118218690156937</v>
+        <v>0.001228234730660915</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.03405432775616646</v>
+        <v>0.002927801106125116</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.08422505110502243</v>
+        <v>0.00712809432297945</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.1141612902283669</v>
+        <v>0.0002345646789763123</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.08440867066383362</v>
+        <v>0.003115098224952817</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.008505193516612053</v>
+        <v>0.0003146455565001816</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.2077368199825287</v>
+        <v>0.005905526224523783</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.1348148137331009</v>
+        <v>0.001610107137821615</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.1136352643370628</v>
+        <v>0.000272448145551607</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.02833636663854122</v>
+        <v>0.001795278629288077</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.006332691758871078</v>
+        <v>0.002056695520877838</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1408792734146118</v>
+        <v>0.00575428968295455</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.04183288291096687</v>
+        <v>0.000146185455378145</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.1473464518785477</v>
+        <v>0.006184342317283154</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.01217279862612486</v>
+        <v>0.001658522756770253</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0428798533976078</v>
+        <v>0.0002270388067699969</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.05410315841436386</v>
+        <v>0.0002646950888447464</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.02797636389732361</v>
+        <v>0.001147759612649679</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.02889786846935749</v>
+        <v>0.0004827133379876614</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.00392381614074111</v>
+        <v>0.0008000298403203487</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.02148021385073662</v>
+        <v>0.002348527777940035</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0144512876868248</v>
+        <v>0.002128390828147531</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0161778274923563</v>
+        <v>0.003332045394927263</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.04488822445273399</v>
+        <v>0.00071223039412871</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.004647332709282637</v>
+        <v>0.0009680278599262238</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.004563460126519203</v>
+        <v>0.001120152766816318</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0144162317737937</v>
+        <v>0.001118456944823265</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.03440455347299576</v>
+        <v>0.002640914637595415</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.03668602555990219</v>
+        <v>0.00362256052903831</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.09178159385919571</v>
+        <v>0.009680246934294701</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.03954223543405533</v>
+        <v>0.003020108211785555</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.03056816942989826</v>
+        <v>0.008181421086192131</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.3189761638641357</v>
+        <v>0.001534226234070957</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.02793086878955364</v>
+        <v>0.005833684466779232</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.1909863501787186</v>
+        <v>0.001012006774544716</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.05161433666944504</v>
+        <v>0.002633048221468925</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.001260915771126747</v>
+        <v>0.008086136542260647</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.05680084973573685</v>
+        <v>0.002576712984591722</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.005032380111515522</v>
+        <v>0.002235724125057459</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.08742877840995789</v>
+        <v>0.001711368793621659</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.009339164942502975</v>
+        <v>0.003364553209394217</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.1348851770162582</v>
+        <v>0.003851961344480515</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.1506161242723465</v>
+        <v>0.001420025015249848</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.2599200308322906</v>
+        <v>0.0005327863618731499</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.02890766784548759</v>
+        <v>0.001862220233306289</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.01363877486437559</v>
+        <v>0.001543901162222028</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.3734717667102814</v>
+        <v>0.002335552591830492</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02440056949853897</v>
+        <v>0.0001174290955532342</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6192867755889893</v>
+        <v>0.0009476493578404188</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01116588711738586</v>
+        <v>0.0004033885488752276</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2698022127151489</v>
+        <v>0.001701469416730106</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08768318593502045</v>
+        <v>0.0005319415358826518</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1937544941902161</v>
+        <v>4.125797931919806e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0119592621922493</v>
+        <v>0.0002575947437435389</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2777176201343536</v>
+        <v>5.329590931069106e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07311658561229706</v>
+        <v>0.002545453608036041</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06544310599565506</v>
+        <v>0.0003271270543336868</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4907117187976837</v>
+        <v>0.0007053004228509963</v>
       </c>
       <c r="M7" t="n">
-        <v>0.248483806848526</v>
+        <v>0.00157226191367954</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3693179488182068</v>
+        <v>0.002852288773283362</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2098398357629776</v>
+        <v>0.0001458514016121626</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1287785470485687</v>
+        <v>0.0001468568807467818</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1222598105669022</v>
+        <v>0.0002663853229023516</v>
       </c>
       <c r="R7" t="n">
-        <v>0.121536523103714</v>
+        <v>7.582965190522373e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0815485343337059</v>
+        <v>0.0007845998625271022</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1488650739192963</v>
+        <v>0.001452202093787491</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03616571426391602</v>
+        <v>0.0002098640543408692</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01611800864338875</v>
+        <v>0.0005940369446761906</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1258724927902222</v>
+        <v>0.0007650880725122988</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1521628350019455</v>
+        <v>5.266822336125188e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0409727543592453</v>
+        <v>0.0001939418580150232</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1293610632419586</v>
+        <v>0.0004802484181709588</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1343368738889694</v>
+        <v>4.640049883164465e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1285628825426102</v>
+        <v>0.001380656496621668</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01105838268995285</v>
+        <v>0.000471894396468997</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.03117383271455765</v>
+        <v>0.0006840121350251138</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1243864893913269</v>
+        <v>2.45046685449779e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1924517750740051</v>
+        <v>0.0002529202902223915</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.1155219450592995</v>
+        <v>0.00110690959263593</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1224907860159874</v>
+        <v>0.000413902394939214</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1059076189994812</v>
+        <v>0.00053363450570032</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.222905308008194</v>
+        <v>0.0002143419114872813</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.04933610185980797</v>
+        <v>0.0002044573484454304</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.141260951757431</v>
+        <v>0.0007990232552401721</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0790230855345726</v>
+        <v>0.000161847347044386</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.06062920391559601</v>
+        <v>4.000357876066118e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1711591482162476</v>
+        <v>0.000164665951160714</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.1232614815235138</v>
+        <v>8.953864744398743e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.07509195804595947</v>
+        <v>6.173140718601644e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.05608630925416946</v>
+        <v>0.0005589947104454041</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.006989751011133194</v>
+        <v>0.0001868411345640197</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.2683199048042297</v>
+        <v>0.0007848221575841308</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.00231851264834404</v>
+        <v>7.101020310074091e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.4321974217891693</v>
+        <v>0.000773297157138586</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.239296942949295</v>
+        <v>0.0008072179043665528</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3564062118530273</v>
+        <v>0.0005545715102925897</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.02699165418744087</v>
+        <v>0.0004805049975402653</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3654672503471375</v>
+        <v>0.000255429302342236</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.468352198600769</v>
+        <v>0.000201895774807781</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.25481116771698</v>
+        <v>0.0001674771192483604</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.2465436309576035</v>
+        <v>7.22860568203032e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03311677277088165</v>
+        <v>0.0001216001401189715</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.09237638860940933</v>
+        <v>8.884433191269636e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1475354433059692</v>
+        <v>0.0001360911119263619</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.4519098699092865</v>
+        <v>0.0001092583406716585</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.3224612772464752</v>
+        <v>1.429102849215269e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1007655784487724</v>
+        <v>8.683202031534165e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.01434840634465218</v>
+        <v>0.000437975162640214</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.006708160042762756</v>
+        <v>4.334251570980996e-05</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.2489908337593079</v>
+        <v>0.0005219895974732935</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0527721531689167</v>
+        <v>0.0001785913773346692</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.01124558597803116</v>
+        <v>0.0004187754529993981</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1612812429666519</v>
+        <v>0.0008959209662862122</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1706331074237823</v>
+        <v>0.0007052692817524076</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02658241242170334</v>
+        <v>0.0003833438968285918</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.09868890047073364</v>
+        <v>0.0003776403609663248</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.1960232257843018</v>
+        <v>0.00020574641530402</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.2219122648239136</v>
+        <v>0.0001764243934303522</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.09268936514854431</v>
+        <v>0.001052303472533822</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01324716210365295</v>
+        <v>0.001281967968679965</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.2409451305866241</v>
+        <v>0.0009399413247592747</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.14431993663311</v>
+        <v>0.000548778276424855</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1269741505384445</v>
+        <v>0.0007627487648278475</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.09042005240917206</v>
+        <v>1.507944398326799e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.2013725340366364</v>
+        <v>0.0001741712912917137</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1444746106863022</v>
+        <v>0.0002005649439524859</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.03091231733560562</v>
+        <v>0.0002877754450310022</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0426749512553215</v>
+        <v>0.0003408039920032024</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.06204906851053238</v>
+        <v>4.893729783361778e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.04886709898710251</v>
+        <v>2.529135053919163e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.04542510956525803</v>
+        <v>0.0002994121750816703</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.03787684068083763</v>
+        <v>0.000583919114433229</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.05418746173381805</v>
+        <v>8.578574124840088e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.03626496344804764</v>
+        <v>8.129221896524541e-06</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.06128984689712524</v>
+        <v>0.0001458621845813468</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0129450848326087</v>
+        <v>0.00014659742009826</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.08189225196838379</v>
+        <v>0.0007043262012302876</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.07094499468803406</v>
+        <v>0.0002145016333088279</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.2433579862117767</v>
+        <v>0.0003674511972349137</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.2957390248775482</v>
+        <v>0.0002178635913878679</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.5092896819114685</v>
+        <v>0.0002614270779304206</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.08164878189563751</v>
+        <v>0.0007033320143818855</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.1182111799716949</v>
+        <v>0.0002846127026714385</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.175529345870018</v>
+        <v>0.0005661158938892186</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.02233467437326908</v>
+        <v>5.147303454577923e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.01146603655070066</v>
+        <v>0.0004006885574199259</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.08377830684185028</v>
+        <v>0.0001497077173553407</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.06202374398708344</v>
+        <v>0.0001559496304253116</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.04053861647844315</v>
+        <v>0.0001276879920624197</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.008485476486384869</v>
+        <v>0.000395766575820744</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.04341521114110947</v>
+        <v>4.868545875069685e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.03611663728952408</v>
+        <v>0.0001323952892562374</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.05254192650318146</v>
+        <v>4.934697062708437e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.06593277305364609</v>
+        <v>7.695978274568915e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1160061657428741</v>
+        <v>0.0004775980778504163</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.06234515830874443</v>
+        <v>0.001542636891826987</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0811057835817337</v>
+        <v>0.0005334292072802782</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.6119852662086487</v>
+        <v>0.0002536206739023328</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1476639211177826</v>
+        <v>0.0006976740551181138</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.1356777399778366</v>
+        <v>0.0007588646258227527</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.04020577296614647</v>
+        <v>0.0007679036352783442</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.1772016286849976</v>
+        <v>0.0004483287339098752</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.1830881386995316</v>
+        <v>0.0001399141474394128</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.1000834852457047</v>
+        <v>0.00058508210349828</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.1573337763547897</v>
+        <v>2.735633643169422e-05</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.03795772790908813</v>
+        <v>0.0005023407284170389</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.1023746430873871</v>
+        <v>2.122727164532989e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.02020306140184402</v>
+        <v>0.001301281037740409</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1411552280187607</v>
+        <v>0.0003157563623972237</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.04590398445725441</v>
+        <v>0.0002929835754912347</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.09002098441123962</v>
+        <v>6.535628926940262e-05</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.01703168451786041</v>
+        <v>0.0003068066143896431</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.02269325032830238</v>
+        <v>5.876243812963367e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.1935711950063705</v>
+        <v>0.0002808593271765858</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.129831925034523</v>
+        <v>0.000283611414488405</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2026900798082352</v>
+        <v>0.0004654276417568326</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.1868937015533447</v>
+        <v>0.0007431379053741693</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.1531244814395905</v>
+        <v>0.0004345045890659094</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.03849146887660027</v>
+        <v>0.0001241212012246251</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.062540203332901</v>
+        <v>0.0003305051941424608</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.1939749121665955</v>
+        <v>0.0002786698751151562</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.004428932443261147</v>
+        <v>0.0004740793083328754</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.1666224747896194</v>
+        <v>0.0002918326645158231</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.1116663888096809</v>
+        <v>9.834519005380571e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.1023842990398407</v>
+        <v>0.0002804719260893762</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1242806389927864</v>
+        <v>0.0006979526951909065</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.09804178029298782</v>
+        <v>7.968913996592164e-05</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.04745003208518028</v>
+        <v>0.0004086876870132983</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.05396634340286255</v>
+        <v>4.526325938059017e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.001857053488492966</v>
+        <v>0.0005286607192829251</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.1537466943264008</v>
+        <v>0.0003035959380213171</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.02543397434055805</v>
+        <v>0.0002128824999090284</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.05645180121064186</v>
+        <v>5.869107189937495e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.08917819708585739</v>
+        <v>0.0003181801293976605</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1780805438756943</v>
+        <v>0.0005363165982998908</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.1880137324333191</v>
+        <v>0.0001557494688313454</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.07422392815351486</v>
+        <v>0.0004670069320127368</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.03303930163383484</v>
+        <v>0.0001950054720509797</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.1188656166195869</v>
+        <v>8.730508852750063e-06</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.004342833533883095</v>
+        <v>0.0004268384946044534</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.03065942414104939</v>
+        <v>0.0001502079830970615</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.03599875420331955</v>
+        <v>0.000231238329433836</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0006719687953591347</v>
+        <v>0.0002041143598034978</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01713012903928757</v>
+        <v>0.0004914076416753232</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.04891376569867134</v>
+        <v>0.0001836062438087538</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.06063785403966904</v>
+        <v>9.010777284856886e-05</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.07822620868682861</v>
+        <v>0.0001570993626955897</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.04299039766192436</v>
+        <v>8.229713421314955e-05</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.01049854978919029</v>
+        <v>0.001614156877622008</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.07133021950721741</v>
+        <v>0.0001065590404323302</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.1679104864597321</v>
+        <v>0.0002473665517754853</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.09945002943277359</v>
+        <v>0.0008254398126155138</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.008429165929555893</v>
+        <v>0.0004653631476685405</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.2385407835245132</v>
+        <v>0.0002726857201196253</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.1031538471579552</v>
+        <v>0.0002577895356807858</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.07234655320644379</v>
+        <v>0.0001215421361848712</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.1131251305341721</v>
+        <v>0.0003744181012734771</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.3329259157180786</v>
+        <v>0.001231778413057327</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.1313802152872086</v>
+        <v>0.0006012322846800089</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.03613793104887009</v>
+        <v>0.00140684493817389</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.07116181403398514</v>
+        <v>0.0003365273878443986</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.1873587667942047</v>
+        <v>0.001305402955040336</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.07085040956735611</v>
+        <v>0.0002373470342718065</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.1815185397863388</v>
+        <v>0.0002378970966674387</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0865018218755722</v>
+        <v>0.0001862219942267984</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.1330033540725708</v>
+        <v>0.0003789734619203955</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.08273576200008392</v>
+        <v>0.0007155853672884405</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.04666991904377937</v>
+        <v>0.0011381262447685</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.1833074688911438</v>
+        <v>0.0001420333719579503</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.06778399646282196</v>
+        <v>0.0005195837584324181</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.1153224408626556</v>
+        <v>0.0001827622181735933</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.07429876923561096</v>
+        <v>0.000491904211230576</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.2078868001699448</v>
+        <v>0.0002303655346622691</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.3976300954818726</v>
+        <v>2.827962453011423e-05</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01825024746358395</v>
+        <v>0.0001091508020181209</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0001224526786245406</v>
+        <v>0.1462527364492416</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001046136720106006</v>
+        <v>0.8308571577072144</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001060452923411503</v>
+        <v>0.07247824221849442</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004149912274442613</v>
+        <v>0.1517178863286972</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001240376150235534</v>
+        <v>0.08826786279678345</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0006989682442508638</v>
+        <v>0.8134012222290039</v>
       </c>
       <c r="G8" t="n">
-        <v>9.187442628899589e-05</v>
+        <v>0.05525484308600426</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001265350147150457</v>
+        <v>0.0975956916809082</v>
       </c>
       <c r="I8" t="n">
-        <v>1.606494879524689e-05</v>
+        <v>0.06753753870725632</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002324197848793119</v>
+        <v>0.09514310956001282</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000902349769603461</v>
+        <v>0.9573206305503845</v>
       </c>
       <c r="L8" t="n">
-        <v>8.594333849032409e-07</v>
+        <v>0.07176387310028076</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0004511681036092341</v>
+        <v>0.2179156541824341</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001564218255225569</v>
+        <v>0.2646470069885254</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000669871224090457</v>
+        <v>0.7817376255989075</v>
       </c>
       <c r="P8" t="n">
-        <v>7.366649515461177e-05</v>
+        <v>0.08400838822126389</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.604256825288758e-05</v>
+        <v>0.03990795463323593</v>
       </c>
       <c r="R8" t="n">
-        <v>1.850774424383417e-06</v>
+        <v>0.0008082948625087738</v>
       </c>
       <c r="S8" t="n">
-        <v>7.291521615115926e-05</v>
+        <v>0.002579331398010254</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001593653432792053</v>
+        <v>0.05195064097642899</v>
       </c>
       <c r="U8" t="n">
-        <v>2.079744808725081e-05</v>
+        <v>0.1646208763122559</v>
       </c>
       <c r="V8" t="n">
-        <v>8.477826486341655e-05</v>
+        <v>0.01007506996393204</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37397755679558e-05</v>
+        <v>0.1424234211444855</v>
       </c>
       <c r="X8" t="n">
-        <v>4.80990820506122e-05</v>
+        <v>0.1826178282499313</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.608996773138642e-05</v>
+        <v>0.2068823724985123</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.764871017774567e-05</v>
+        <v>0.1981344521045685</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0001159167004516348</v>
+        <v>0.00781854335218668</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.091245212592185e-05</v>
+        <v>0.035147525370121</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0001061706352629699</v>
+        <v>0.2173228561878204</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.960803976748139e-05</v>
+        <v>0.124572291970253</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.214947016909719e-06</v>
+        <v>0.3648062944412231</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0001067116972990334</v>
+        <v>0.03631946444511414</v>
       </c>
       <c r="AG8" t="n">
-        <v>8.020763925742358e-05</v>
+        <v>0.2048512697219849</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0001096468040486798</v>
+        <v>0.09457740187644958</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.505447188625112e-05</v>
+        <v>0.3418589234352112</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8.470861939713359e-05</v>
+        <v>0.127378523349762</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.034326750319451e-05</v>
+        <v>0.03027942217886448</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.000156230860739015</v>
+        <v>0.191576287150383</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.443748078600038e-05</v>
+        <v>0.05626837909221649</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.418938573915511e-05</v>
+        <v>0.03027231991291046</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0001031169231282547</v>
+        <v>0.06988031417131424</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0001378595479764044</v>
+        <v>0.1450573801994324</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.037657395703718e-06</v>
+        <v>0.1508107483386993</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.389520422089845e-06</v>
+        <v>0.1480018645524979</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0001655897649470717</v>
+        <v>0.1021702140569687</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0001042667136061937</v>
+        <v>0.0390850193798542</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.000626101391389966</v>
+        <v>0.6418707370758057</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.218371759634465e-05</v>
+        <v>0.1388300657272339</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.072219184716232e-05</v>
+        <v>0.06832829862833023</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.00964170997031e-05</v>
+        <v>0.3710189163684845</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004441572527866811</v>
+        <v>0.5425690412521362</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.121171802282333e-05</v>
+        <v>0.03401225060224533</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.234297087648883e-06</v>
+        <v>0.06344949454069138</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0002753192675299942</v>
+        <v>0.01142968703061342</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0001321594318142161</v>
+        <v>0.06095925718545914</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002055751392617822</v>
+        <v>0.1866016685962677</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0002075783413602039</v>
+        <v>0.1548754274845123</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0001257046678801998</v>
+        <v>0.2120497226715088</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0002726317616179585</v>
+        <v>0.2528584003448486</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0002221215108875185</v>
+        <v>0.1356653422117233</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0001584174315212294</v>
+        <v>0.1180106401443481</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.497187809552997e-05</v>
+        <v>0.1427913755178452</v>
       </c>
       <c r="BK8" t="n">
-        <v>9.416548709850758e-05</v>
+        <v>0.06159806996583939</v>
       </c>
       <c r="BL8" t="n">
-        <v>9.696482266008388e-06</v>
+        <v>0.1193046271800995</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.009665993478848e-05</v>
+        <v>0.0370294600725174</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0001111999590648338</v>
+        <v>0.04511052742600441</v>
       </c>
       <c r="BO8" t="n">
-        <v>6.224910612218082e-05</v>
+        <v>0.03634857386350632</v>
       </c>
       <c r="BP8" t="n">
-        <v>7.477993494831026e-05</v>
+        <v>0.1092572212219238</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.247744360938668e-05</v>
+        <v>0.1241497695446014</v>
       </c>
       <c r="BR8" t="n">
-        <v>2.916789162554778e-05</v>
+        <v>0.1031661480665207</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.855069058365189e-05</v>
+        <v>0.06279474496841431</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.621881089406088e-06</v>
+        <v>0.09580737352371216</v>
       </c>
       <c r="BU8" t="n">
-        <v>7.385452772723511e-05</v>
+        <v>0.03366448730230331</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.000325496046571061</v>
+        <v>0.3557608723640442</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.26290376810357e-05</v>
+        <v>0.1579908281564713</v>
       </c>
       <c r="BX8" t="n">
-        <v>9.195355960400775e-05</v>
+        <v>0.0003280015662312508</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.37379998806864e-05</v>
+        <v>0.1236511915922165</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0001094224426196888</v>
+        <v>0.3981504142284393</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.940821549505927e-06</v>
+        <v>0.2523137927055359</v>
       </c>
       <c r="CB8" t="n">
-        <v>1.370510562992422e-05</v>
+        <v>0.06079284101724625</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0001211780472658575</v>
+        <v>0.05562398210167885</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.658210385357961e-05</v>
+        <v>0.02502915449440479</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0001891161809908226</v>
+        <v>0.2849177122116089</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0001065008837031201</v>
+        <v>0.008847317658364773</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.894564335700125e-05</v>
+        <v>0.03156503289937973</v>
       </c>
       <c r="CH8" t="n">
-        <v>4.011255805380642e-05</v>
+        <v>0.02359034493565559</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0001166874717455357</v>
+        <v>0.2105191349983215</v>
       </c>
       <c r="CJ8" t="n">
-        <v>6.473476241808385e-05</v>
+        <v>0.02052813395857811</v>
       </c>
       <c r="CK8" t="n">
-        <v>2.604784822324291e-05</v>
+        <v>0.006298176944255829</v>
       </c>
       <c r="CL8" t="n">
-        <v>7.012967398623005e-05</v>
+        <v>0.009370062500238419</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0001123603287851438</v>
+        <v>0.1789374351501465</v>
       </c>
       <c r="CN8" t="n">
-        <v>5.734355363529176e-05</v>
+        <v>0.4383108019828796</v>
       </c>
       <c r="CO8" t="n">
-        <v>4.966219421476126e-06</v>
+        <v>0.3003302812576294</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0001158876402769238</v>
+        <v>0.1011921986937523</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.48585742560681e-05</v>
+        <v>0.04410061240196228</v>
       </c>
       <c r="CR8" t="n">
-        <v>4.305111724534072e-05</v>
+        <v>0.2187859863042831</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0001689849450485781</v>
+        <v>0.07138168811798096</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0001604507560841739</v>
+        <v>0.1178365647792816</v>
       </c>
       <c r="CU8" t="n">
-        <v>3.869268766720779e-06</v>
+        <v>0.05253452062606812</v>
       </c>
       <c r="CV8" t="n">
-        <v>5.841876372869592e-06</v>
+        <v>0.005745869129896164</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0001764962071320042</v>
+        <v>0.2650851905345917</v>
       </c>
       <c r="CX8" t="n">
-        <v>9.737213258631527e-05</v>
+        <v>0.01853507570922375</v>
       </c>
       <c r="CY8" t="n">
-        <v>8.272804552689195e-05</v>
+        <v>0.03703401237726212</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.944983447785489e-05</v>
+        <v>0.007324792444705963</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0001380805770168081</v>
+        <v>0.202046811580658</v>
       </c>
       <c r="DB8" t="n">
-        <v>6.546812073793262e-05</v>
+        <v>0.004041978623718023</v>
       </c>
       <c r="DC8" t="n">
-        <v>6.156801828183234e-05</v>
+        <v>0.01659712940454483</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.339126462582499e-05</v>
+        <v>0.0001458488404750824</v>
       </c>
       <c r="DE8" t="n">
-        <v>3.939459202229045e-05</v>
+        <v>0.2469816952943802</v>
       </c>
       <c r="DF8" t="n">
-        <v>9.438629786018282e-05</v>
+        <v>0.02841364219784737</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.504543251940049e-05</v>
+        <v>0.1246482655405998</v>
       </c>
       <c r="DH8" t="n">
-        <v>4.672164868679829e-05</v>
+        <v>0.02980853617191315</v>
       </c>
       <c r="DI8" t="n">
-        <v>4.11181608797051e-05</v>
+        <v>0.07448233664035797</v>
       </c>
       <c r="DJ8" t="n">
-        <v>8.519014954799786e-05</v>
+        <v>0.3401063978672028</v>
       </c>
       <c r="DK8" t="n">
-        <v>9.088130900636315e-05</v>
+        <v>0.1386427879333496</v>
       </c>
       <c r="DL8" t="n">
-        <v>7.517910125898197e-05</v>
+        <v>0.1191722601652145</v>
       </c>
       <c r="DM8" t="n">
-        <v>5.729973418056034e-05</v>
+        <v>0.1697571873664856</v>
       </c>
       <c r="DN8" t="n">
-        <v>4.300031650927849e-05</v>
+        <v>0.02598973736166954</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.476176425465383e-05</v>
+        <v>0.1940572261810303</v>
       </c>
       <c r="DP8" t="n">
-        <v>7.074294990161434e-05</v>
+        <v>0.035362608730793</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0001171798066934571</v>
+        <v>0.1086021363735199</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.202410440891981e-05</v>
+        <v>0.03145742043852806</v>
       </c>
       <c r="DS8" t="n">
-        <v>2.389012115600053e-05</v>
+        <v>0.05981237068772316</v>
       </c>
       <c r="DT8" t="n">
-        <v>2.269756441819482e-05</v>
+        <v>0.06066429987549782</v>
       </c>
       <c r="DU8" t="n">
-        <v>5.348460035747848e-06</v>
+        <v>0.05105486512184143</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0001250272325705737</v>
+        <v>0.03421902656555176</v>
       </c>
       <c r="DW8" t="n">
-        <v>5.656565917888656e-05</v>
+        <v>0.04093477874994278</v>
       </c>
       <c r="DX8" t="n">
-        <v>4.711550354841165e-05</v>
+        <v>0.2239405512809753</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0001039552735164762</v>
+        <v>0.01973819360136986</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1.598816197656561e-06</v>
+        <v>0.01992430724203587</v>
       </c>
       <c r="EA8" t="n">
-        <v>6.437984120566398e-05</v>
+        <v>0.1563889980316162</v>
       </c>
       <c r="EB8" t="n">
-        <v>3.609657505876385e-05</v>
+        <v>0.03970005363225937</v>
       </c>
       <c r="EC8" t="n">
-        <v>4.075304605066776e-05</v>
+        <v>0.006297698244452477</v>
       </c>
       <c r="ED8" t="n">
-        <v>1.021362550090998e-08</v>
+        <v>0.1494331210851669</v>
       </c>
       <c r="EE8" t="n">
-        <v>4.411307600094005e-06</v>
+        <v>0.2120168507099152</v>
       </c>
       <c r="EF8" t="n">
-        <v>1.810756657505408e-05</v>
+        <v>0.009830567985773087</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0001352526160189882</v>
+        <v>0.09754346311092377</v>
       </c>
       <c r="EH8" t="n">
-        <v>7.79512120061554e-05</v>
+        <v>0.08027196675539017</v>
       </c>
       <c r="EI8" t="n">
-        <v>9.773825877346098e-05</v>
+        <v>0.02355099096894264</v>
       </c>
       <c r="EJ8" t="n">
-        <v>3.183556327712722e-05</v>
+        <v>0.03720440715551376</v>
       </c>
       <c r="EK8" t="n">
-        <v>7.56749723223038e-05</v>
+        <v>0.1646712869405746</v>
       </c>
       <c r="EL8" t="n">
-        <v>7.387273944914341e-05</v>
+        <v>0.04848406463861465</v>
       </c>
       <c r="EM8" t="n">
-        <v>8.39751010062173e-06</v>
+        <v>0.05733426660299301</v>
       </c>
       <c r="EN8" t="n">
-        <v>2.15222971746698e-05</v>
+        <v>0.006589706055819988</v>
       </c>
       <c r="EO8" t="n">
-        <v>6.817794201197103e-06</v>
+        <v>0.02033055573701859</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0001440757914679125</v>
+        <v>0.1501873135566711</v>
       </c>
       <c r="EQ8" t="n">
-        <v>9.72710331552662e-05</v>
+        <v>0.1087322980165482</v>
       </c>
       <c r="ER8" t="n">
-        <v>1.566372156958096e-05</v>
+        <v>0.01140980795025826</v>
       </c>
       <c r="ES8" t="n">
-        <v>4.217774403514341e-05</v>
+        <v>0.138874426484108</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0001920483191497624</v>
+        <v>0.112679198384285</v>
       </c>
       <c r="EU8" t="n">
-        <v>6.895424303365871e-05</v>
+        <v>0.006344268098473549</v>
       </c>
       <c r="EV8" t="n">
-        <v>8.810976578388363e-05</v>
+        <v>0.054987832903862</v>
       </c>
       <c r="EW8" t="n">
-        <v>3.243365790694952e-05</v>
+        <v>0.03687579557299614</v>
       </c>
       <c r="EX8" t="n">
-        <v>1.112623886001529e-05</v>
+        <v>0.01523188315331936</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0001772343821357936</v>
+        <v>0.2759495377540588</v>
       </c>
       <c r="EZ8" t="n">
-        <v>6.942758045624942e-05</v>
+        <v>0.01754092052578926</v>
       </c>
       <c r="FA8" t="n">
-        <v>5.439750384539366e-05</v>
+        <v>0.01190934423357248</v>
       </c>
       <c r="FB8" t="n">
-        <v>4.569345765048638e-05</v>
+        <v>0.0565289631485939</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0001032492509693839</v>
+        <v>0.2043487578630447</v>
       </c>
       <c r="FD8" t="n">
-        <v>7.316787377931178e-05</v>
+        <v>0.02720333822071552</v>
       </c>
       <c r="FE8" t="n">
-        <v>2.269505603180733e-05</v>
+        <v>0.01465877052396536</v>
       </c>
       <c r="FF8" t="n">
-        <v>7.509358692914248e-05</v>
+        <v>0.03743430972099304</v>
       </c>
       <c r="FG8" t="n">
-        <v>7.337835086218547e-06</v>
+        <v>0.07815681397914886</v>
       </c>
       <c r="FH8" t="n">
-        <v>8.205626363633201e-05</v>
+        <v>0.0262400284409523</v>
       </c>
       <c r="FI8" t="n">
-        <v>8.696231816429645e-05</v>
+        <v>0.06034278869628906</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0001559840311529115</v>
+        <v>0.05081593990325928</v>
       </c>
       <c r="FK8" t="n">
-        <v>5.333118315320462e-05</v>
+        <v>0.1267165243625641</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0001005382000585087</v>
+        <v>0.2171245217323303</v>
       </c>
       <c r="FM8" t="n">
-        <v>1.986865390790626e-05</v>
+        <v>0.1251229792833328</v>
       </c>
       <c r="FN8" t="n">
-        <v>2.342653533560224e-05</v>
+        <v>0.05685148388147354</v>
       </c>
       <c r="FO8" t="n">
-        <v>8.274259744212031e-05</v>
+        <v>0.1442191749811172</v>
       </c>
       <c r="FP8" t="n">
-        <v>3.658493369584903e-05</v>
+        <v>0.3243410587310791</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0002992851077578962</v>
+        <v>0.05158866569399834</v>
       </c>
       <c r="FR8" t="n">
-        <v>6.980296893743798e-05</v>
+        <v>0.07584426552057266</v>
       </c>
       <c r="FS8" t="n">
-        <v>6.889191718073562e-05</v>
+        <v>0.02095167711377144</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.000134896079543978</v>
+        <v>0.02623035572469234</v>
       </c>
       <c r="FU8" t="n">
-        <v>2.409440639894456e-06</v>
+        <v>0.08591940253973007</v>
       </c>
       <c r="FV8" t="n">
-        <v>2.218412373622414e-05</v>
+        <v>0.008117187768220901</v>
       </c>
       <c r="FW8" t="n">
-        <v>2.523665716580581e-05</v>
+        <v>0.0846284031867981</v>
       </c>
       <c r="FX8" t="n">
-        <v>4.385400461615063e-05</v>
+        <v>0.07173210382461548</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0001485062239225954</v>
+        <v>0.1070414707064629</v>
       </c>
       <c r="FZ8" t="n">
-        <v>6.567404852830805e-06</v>
+        <v>0.06662537902593613</v>
       </c>
       <c r="GA8" t="n">
-        <v>1.406733281328343e-05</v>
+        <v>0.08102867007255554</v>
       </c>
       <c r="GB8" t="n">
-        <v>4.770705345435999e-06</v>
+        <v>0.02144121006131172</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0002016162616200745</v>
+        <v>0.3177976608276367</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0001098449574783444</v>
+        <v>0.1831642687320709</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0003340897965244949</v>
+        <v>0.1058195158839226</v>
       </c>
       <c r="GF8" t="n">
-        <v>3.683641989482567e-05</v>
+        <v>0.06355041265487671</v>
       </c>
       <c r="GG8" t="n">
-        <v>4.472676664590836e-05</v>
+        <v>0.05011739954352379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.02931602485477924</v>
+        <v>0.0007193200290203094</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2559750378131866</v>
+        <v>0.8547157049179077</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02510257810354233</v>
+        <v>0.04774463176727295</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1712604314088821</v>
+        <v>0.7514524459838867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05169974640011787</v>
+        <v>0.11986343562603</v>
       </c>
       <c r="F9" t="n">
-        <v>0.112721212208271</v>
+        <v>0.1340846717357635</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04048885032534599</v>
+        <v>0.2874619662761688</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00586932897567749</v>
+        <v>0.02702201344072819</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03439148142933846</v>
+        <v>0.166889950633049</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02659811079502106</v>
+        <v>0.03103850781917572</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2403471022844315</v>
+        <v>1.067376971244812</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005906415637582541</v>
+        <v>0.03606376051902771</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1340620070695877</v>
+        <v>0.8265758752822876</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04014848917722702</v>
+        <v>0.03675143420696259</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05290353670716286</v>
+        <v>0.03922789543867111</v>
       </c>
       <c r="P9" t="n">
-        <v>0.047508854418993</v>
+        <v>0.02720233798027039</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06733518093824387</v>
+        <v>0.1707518547773361</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04619281738996506</v>
+        <v>0.2744296193122864</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0212935246527195</v>
+        <v>0.1654844582080841</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02326912805438042</v>
+        <v>0.04424409568309784</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0262223482131958</v>
+        <v>0.04896575212478638</v>
       </c>
       <c r="V9" t="n">
-        <v>0.05357512086629868</v>
+        <v>0.02986879274249077</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03666624799370766</v>
+        <v>0.07496391236782074</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01429185271263123</v>
+        <v>0.09344200044870377</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02619067952036858</v>
+        <v>0.01940240152180195</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04202765598893166</v>
+        <v>0.1230013072490692</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0423721931874752</v>
+        <v>0.1715726554393768</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0391940101981163</v>
+        <v>0.0987689346075058</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.005420637782663107</v>
+        <v>0.03447764366865158</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0360153466463089</v>
+        <v>0.001584798097610474</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02176372893154621</v>
+        <v>0.03837423026561737</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007657007314264774</v>
+        <v>0.210795521736145</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.006648550741374493</v>
+        <v>0.283195436000824</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0134025514125824</v>
+        <v>0.2790080606937408</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.004577761515974998</v>
+        <v>0.1154528111219406</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.03640030324459076</v>
+        <v>0.04649649187922478</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.005298059899359941</v>
+        <v>0.1481873840093613</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04940728843212128</v>
+        <v>0.3212761878967285</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.02841380424797535</v>
+        <v>0.04328904300928116</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.01273765694350004</v>
+        <v>0.05947063863277435</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.02571777999401093</v>
+        <v>0.4440849125385284</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.03350675478577614</v>
+        <v>0.04082567244768143</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002086644992232323</v>
+        <v>0.01120320707559586</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.03398735076189041</v>
+        <v>0.09717545658349991</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.03504842147231102</v>
+        <v>0.07217618077993393</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.08006210625171661</v>
+        <v>0.03670887649059296</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1389434933662415</v>
+        <v>0.4245503544807434</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.02726925350725651</v>
+        <v>0.05140190944075584</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.107305184006691</v>
+        <v>0.1746544241905212</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.05994824320077896</v>
+        <v>0.08076926320791245</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.08248541504144669</v>
+        <v>0.01477456465363503</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.02300363034009933</v>
+        <v>0.0054891686886549</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.06912727653980255</v>
+        <v>0.1073604971170425</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.08303093910217285</v>
+        <v>0.1491610258817673</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.02134568244218826</v>
+        <v>0.0004061758518218994</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03630122169852257</v>
+        <v>0.1272116005420685</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.04186470806598663</v>
+        <v>0.08632967621088028</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.008574570529162884</v>
+        <v>0.00538591668009758</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.02250803075730801</v>
+        <v>0.0004527447745203972</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001877356320619583</v>
+        <v>0.05068002641201019</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.03385842218995094</v>
+        <v>0.08980230242013931</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.001455694437026978</v>
+        <v>0.07910275459289551</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01703175902366638</v>
+        <v>0.02506396733224392</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.02996223419904709</v>
+        <v>0.01393376477062702</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.01869837008416653</v>
+        <v>0.2420144081115723</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0130696389824152</v>
+        <v>0.1417962461709976</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.00571329053491354</v>
+        <v>0.1126560270786285</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01532755047082901</v>
+        <v>0.1288288533687592</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01967094466090202</v>
+        <v>0.03823976218700409</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01393045764416456</v>
+        <v>0.09303354471921921</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.000329374335706234</v>
+        <v>0.01372769847512245</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.000470377504825592</v>
+        <v>0.04118660092353821</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.05646296963095665</v>
+        <v>0.06762447953224182</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0846027210354805</v>
+        <v>0.439788818359375</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01800921559333801</v>
+        <v>0.1092986091971397</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.08666279911994934</v>
+        <v>0.3209518194198608</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02414969354867935</v>
+        <v>0.1758415848016739</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0210577379912138</v>
+        <v>0.07504461705684662</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.009858814999461174</v>
+        <v>0.02473406493663788</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.04579908400774002</v>
+        <v>0.07378826290369034</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.04888546839356422</v>
+        <v>0.2224989980459213</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.005708066746592522</v>
+        <v>0.001619422808289528</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.02531887404620647</v>
+        <v>0.3237979114055634</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0205483753234148</v>
+        <v>0.03775103390216827</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0293061975389719</v>
+        <v>0.2614889740943909</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.006626751739531755</v>
+        <v>0.09588324278593063</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01186443120241165</v>
+        <v>0.04218786582350731</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.006139715202152729</v>
+        <v>0.001389898359775543</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00239174859598279</v>
+        <v>0.01419221796095371</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.02835612930357456</v>
+        <v>0.04324700310826302</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.03833840042352676</v>
+        <v>0.09627581387758255</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.03006379306316376</v>
+        <v>0.4465708136558533</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.01733850128948689</v>
+        <v>0.2376068085432053</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.00505276070907712</v>
+        <v>0.2901078462600708</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01798533275723457</v>
+        <v>0.2170837819576263</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.005196861922740936</v>
+        <v>0.03037737868726254</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.06445342302322388</v>
+        <v>0.2435663044452667</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.04709206521511078</v>
+        <v>0.1000037863850594</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.006103432271629572</v>
+        <v>0.1382874697446823</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.006061101797968149</v>
+        <v>0.01971953175961971</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.03591514006257057</v>
+        <v>0.3278940320014954</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.02041670307517052</v>
+        <v>0.02762872353196144</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.03622222691774368</v>
+        <v>0.2367449998855591</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.003694526851177216</v>
+        <v>0.05718689411878586</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02192843146622181</v>
+        <v>0.01471261586993933</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.009797999635338783</v>
+        <v>0.006803448311984539</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.009438769891858101</v>
+        <v>0.03216230869293213</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.02273339778184891</v>
+        <v>0.01451928168535233</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.01969312317669392</v>
+        <v>0.04364462941884995</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.06303528696298599</v>
+        <v>0.02985045313835144</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.006238999776542187</v>
+        <v>0.3066389560699463</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.09708442538976669</v>
+        <v>0.1174857467412949</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02863574214279652</v>
+        <v>0.2146641314029694</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0002962462604045868</v>
+        <v>0.3159712553024292</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.01754215359687805</v>
+        <v>0.09560961276292801</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.04130116105079651</v>
+        <v>0.236921489238739</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.003542195539921522</v>
+        <v>0.04075166955590248</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.01791027747094631</v>
+        <v>0.003140597138553858</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0317765399813652</v>
+        <v>0.1965350657701492</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.05217690765857697</v>
+        <v>0.06046078354120255</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.02350210398435593</v>
+        <v>0.2166936993598938</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.01537628471851349</v>
+        <v>0.02122546546161175</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.04329799860715866</v>
+        <v>0.03087430074810982</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.005054139532148838</v>
+        <v>0.1118379458785057</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0002796546323224902</v>
+        <v>0.007837747223675251</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.05934099107980728</v>
+        <v>0.344611257314682</v>
       </c>
       <c r="DW9" t="n">
-        <v>4.815682768821716e-05</v>
+        <v>0.002212308812886477</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.01063252799212933</v>
+        <v>0.1066914051771164</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.04710192605853081</v>
+        <v>0.01938453130424023</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.03792004287242889</v>
+        <v>0.1677152514457703</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.04838249087333679</v>
+        <v>0.01630969345569611</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.01768293976783752</v>
+        <v>0.259025901556015</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.001553724287077785</v>
+        <v>0.2400957345962524</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001410203520208597</v>
+        <v>0.4674828052520752</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.005089435260742903</v>
+        <v>0.2141342610120773</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.00464473944157362</v>
+        <v>0.05541529133915901</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0118378484621644</v>
+        <v>0.3094885945320129</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.02866489253938198</v>
+        <v>0.119081549346447</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.01752758584916592</v>
+        <v>0.2172882109880447</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.008044538088142872</v>
+        <v>0.08393903076648712</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.04818077757954597</v>
+        <v>0.08577487617731094</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.006031384691596031</v>
+        <v>0.0681123360991478</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.01741859316825867</v>
+        <v>0.02529759705066681</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.006650636438280344</v>
+        <v>0.1926165521144867</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.007157644256949425</v>
+        <v>0.08663347363471985</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.02820553444325924</v>
+        <v>0.2977259755134583</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.039200060069561</v>
+        <v>0.05345495045185089</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.007124298252165318</v>
+        <v>0.1409611701965332</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.03677432239055634</v>
+        <v>0.08470668643712997</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.09763763844966888</v>
+        <v>0.2759737074375153</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.03928472474217415</v>
+        <v>0.15365369617939</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.02243796363472939</v>
+        <v>0.1110252067446709</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.005198713392019272</v>
+        <v>0.1597028225660324</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.002976646646857262</v>
+        <v>0.008748870342969894</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0287212859839201</v>
+        <v>0.3243190050125122</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.008507048711180687</v>
+        <v>0.003222312778234482</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.03442085161805153</v>
+        <v>0.2831166386604309</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.002905137138441205</v>
+        <v>0.09460766613483429</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.009272493422031403</v>
+        <v>0.05949154123663902</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.01874273642897606</v>
+        <v>0.005702037364244461</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.001346973702311516</v>
+        <v>0.05946862697601318</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.02928321994841099</v>
+        <v>0.02264697290956974</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.009951256215572357</v>
+        <v>0.009879039600491524</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001231512520462275</v>
+        <v>0.0106048509478569</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.01040364429354668</v>
+        <v>0.1595398485660553</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.009545784443616867</v>
+        <v>0.02249361574649811</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.02566322684288025</v>
+        <v>0.3268352746963501</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.02236183732748032</v>
+        <v>0.06327815353870392</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.006501747760921717</v>
+        <v>0.06386691331863403</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.01244063675403595</v>
+        <v>0.3052271008491516</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.01253874599933624</v>
+        <v>0.2651969194412231</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.03577987849712372</v>
+        <v>0.01590371876955032</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0606653019785881</v>
+        <v>0.01318235695362091</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.02987411804497242</v>
+        <v>0.08852040022611618</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.07053043693304062</v>
+        <v>0.1383237689733505</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0330728143453598</v>
+        <v>0.2783768773078918</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01312750857323408</v>
+        <v>0.2281544208526611</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.01215015724301338</v>
+        <v>0.1247220039367676</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.009923426434397697</v>
+        <v>0.2002065181732178</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.001471253111958504</v>
+        <v>0.2506974339485168</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.02805379405617714</v>
+        <v>0.01240324974060059</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.002324323635548353</v>
+        <v>0.2291703373193741</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.02624045312404633</v>
+        <v>0.20750892162323</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.02638378366827965</v>
+        <v>0.393764853477478</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0776946172118187</v>
+        <v>0.03390893340110779</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0222325436770916</v>
+        <v>0.1307398527860641</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.09915392845869064</v>
+        <v>0.3060555160045624</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.02979398332536221</v>
+        <v>0.08364696800708771</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.009096654132008553</v>
+        <v>0.005716155748814344</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9.29248271859251e-05</v>
+        <v>0.0002094632363878191</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0009602078353054821</v>
+        <v>0.002243402879685163</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001190242182929069</v>
+        <v>0.0005995201645419002</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0004263363662175834</v>
+        <v>0.000706005550455302</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001209976326208562</v>
+        <v>0.0009172103018499911</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0002121913566952571</v>
+        <v>0.0008605564362369478</v>
       </c>
       <c r="G10" t="n">
-        <v>4.45679179392755e-05</v>
+        <v>0.0002954551600851119</v>
       </c>
       <c r="H10" t="n">
-        <v>2.843296351784375e-05</v>
+        <v>5.984532253933139e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>4.424458529683761e-05</v>
+        <v>0.0002518366673029959</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001526145933894441</v>
+        <v>5.223730113357306e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0006861532456241548</v>
+        <v>0.002790102735161781</v>
       </c>
       <c r="L10" t="n">
-        <v>8.304520633828361e-06</v>
+        <v>0.000690336455591023</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0004016170569229871</v>
+        <v>0.001294308807700872</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002037122030742466</v>
+        <v>0.001423322595655918</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0002124122111126781</v>
+        <v>0.0002507695462554693</v>
       </c>
       <c r="P10" t="n">
-        <v>1.832617635955103e-05</v>
+        <v>0.0001628030295250937</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.67567359819077e-05</v>
+        <v>0.0007867505773901939</v>
       </c>
       <c r="R10" t="n">
-        <v>9.36440919758752e-05</v>
+        <v>0.0001995047641685233</v>
       </c>
       <c r="S10" t="n">
-        <v>1.345440523436991e-05</v>
+        <v>5.579168282565661e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0001241357676917687</v>
+        <v>8.597397390985861e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>3.131398625555448e-05</v>
+        <v>0.0001028755941661075</v>
       </c>
       <c r="V10" t="n">
-        <v>8.925217116484419e-05</v>
+        <v>0.0003057622234337032</v>
       </c>
       <c r="W10" t="n">
-        <v>2.913844582508318e-05</v>
+        <v>0.0003417276020627469</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0001293906097998843</v>
+        <v>0.0003551479312591255</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.577553722308949e-05</v>
+        <v>0.0003544721112120897</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.061162376776338e-06</v>
+        <v>0.0001040086790453643</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.220952491275966e-05</v>
+        <v>0.0003023816971108317</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.746399670490064e-05</v>
+        <v>0.0002347049885429442</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.000162256445037201</v>
+        <v>0.0005821312661282718</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.317101487074979e-05</v>
+        <v>0.0001883775257738307</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.004857131192693e-05</v>
+        <v>0.0004284632159397006</v>
       </c>
       <c r="AF10" t="n">
-        <v>7.959078357089311e-05</v>
+        <v>0.0002145180042134598</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.11145912646316e-05</v>
+        <v>0.0005083575961180031</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.683660467388108e-05</v>
+        <v>3.0757553759031e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.375468077138066e-05</v>
+        <v>0.0003718531806953251</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.900439984747209e-06</v>
+        <v>3.619226481532678e-05</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.525862070498988e-05</v>
+        <v>9.097183647099882e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>9.243221575161442e-05</v>
+        <v>0.0007307152263820171</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.428309587936383e-05</v>
+        <v>9.775651415111497e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.590852429624647e-05</v>
+        <v>0.0003324970894027501</v>
       </c>
       <c r="AO10" t="n">
-        <v>6.764299178030342e-05</v>
+        <v>0.0003616597678046674</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0001315701229032129</v>
+        <v>0.0003171462740283459</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.141619006579276e-05</v>
+        <v>0.0001202601997647434</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.773724842583761e-05</v>
+        <v>0.0001808773376978934</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.257036147871986e-05</v>
+        <v>2.945276173704769e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.807096825563349e-05</v>
+        <v>1.875818998087198e-05</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0005754437297582626</v>
+        <v>0.002697050338611007</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.231139271520078e-05</v>
+        <v>0.0001144661073340103</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.661264261405449e-05</v>
+        <v>0.000316101941280067</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.071483171079308e-05</v>
+        <v>0.0007065877434797585</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.514610165846534e-05</v>
+        <v>0.0002492047497071326</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.533172275638208e-05</v>
+        <v>0.0001302799500990659</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0001081355439964682</v>
+        <v>0.0003111324040219188</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.403861723607406e-05</v>
+        <v>0.0001554808113723993</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.525364784058183e-05</v>
+        <v>9.204899834003299e-05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0001508274144725874</v>
+        <v>0.0006302886758930981</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0001522255188319832</v>
+        <v>0.0005096944514662027</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.000144451652886346</v>
+        <v>0.0002420820819679648</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0002893315686378628</v>
+        <v>0.0001727728667901829</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0001081589289242402</v>
+        <v>0.0003274703631177545</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0001037025067489594</v>
+        <v>0.0001310824154643342</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0001149271047324874</v>
+        <v>5.408524157246575e-05</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.037954593310133e-05</v>
+        <v>0.0002451537584420294</v>
       </c>
       <c r="BL10" t="n">
-        <v>6.811328057665378e-05</v>
+        <v>0.0001405490620527416</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.833205457543954e-05</v>
+        <v>0.0003008254570886493</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.46859043627046e-05</v>
+        <v>0.0001573743793414906</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.234734660713002e-05</v>
+        <v>0.0001644599251449108</v>
       </c>
       <c r="BP10" t="n">
-        <v>7.811940304236487e-05</v>
+        <v>0.0006351514020934701</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.143951031845063e-05</v>
+        <v>0.0003165141097269952</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0001153004996012896</v>
+        <v>0.0004105855477973819</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.678382538259029e-05</v>
+        <v>3.826694410236087e-07</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.912634878768586e-05</v>
+        <v>0.0001111475430661812</v>
       </c>
       <c r="BU10" t="n">
-        <v>2.997397314175032e-05</v>
+        <v>0.0001036812900565565</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0002911311748903245</v>
+        <v>0.001529092667624354</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.1198952102568e-05</v>
+        <v>2.756598041742109e-05</v>
       </c>
       <c r="BX10" t="n">
-        <v>5.011458051740192e-05</v>
+        <v>0.0007146753487177193</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.724799585645087e-05</v>
+        <v>0.0002796689514070749</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0001156676662503742</v>
+        <v>0.0002708844840526581</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.6647785489331e-05</v>
+        <v>0.0004204059659969062</v>
       </c>
       <c r="CB10" t="n">
-        <v>1.269885797228198e-05</v>
+        <v>9.641813085181639e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.174995021661744e-05</v>
+        <v>0.0002202779578510672</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.370664515183307e-05</v>
+        <v>9.530465467832983e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0001725475594867021</v>
+        <v>0.0008387462003156543</v>
       </c>
       <c r="CF10" t="n">
-        <v>4.992624599253759e-05</v>
+        <v>0.0001680474088061601</v>
       </c>
       <c r="CG10" t="n">
-        <v>4.33750064985361e-05</v>
+        <v>0.0002485437726136297</v>
       </c>
       <c r="CH10" t="n">
-        <v>5.779601269750856e-05</v>
+        <v>0.0001959566288860515</v>
       </c>
       <c r="CI10" t="n">
-        <v>3.433287929510698e-05</v>
+        <v>0.0001764290063874796</v>
       </c>
       <c r="CJ10" t="n">
-        <v>5.756120299338363e-05</v>
+        <v>3.413519152672961e-06</v>
       </c>
       <c r="CK10" t="n">
-        <v>8.432678441749886e-06</v>
+        <v>5.607714774669148e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.707423507468775e-05</v>
+        <v>0.0001269446656806394</v>
       </c>
       <c r="CM10" t="n">
-        <v>9.441334987059236e-05</v>
+        <v>0.0002426233841106296</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.389423116255784e-06</v>
+        <v>0.001484859734773636</v>
       </c>
       <c r="CO10" t="n">
-        <v>2.924538421211764e-05</v>
+        <v>0.0002717701427172869</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0001140327585744672</v>
+        <v>0.0004547963326331228</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0001272347290068865</v>
+        <v>6.452525121858343e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0001427859533578157</v>
+        <v>2.695201692404225e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>5.015061469748616e-05</v>
+        <v>3.89576016459614e-05</v>
       </c>
       <c r="CT10" t="n">
-        <v>4.732814340968616e-05</v>
+        <v>2.649528323672712e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>2.986874096677639e-05</v>
+        <v>9.955192945199087e-05</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.075573138426989e-05</v>
+        <v>2.038292223005556e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0001575856149429455</v>
+        <v>0.0008198407595045865</v>
       </c>
       <c r="CX10" t="n">
-        <v>6.020695946062915e-05</v>
+        <v>0.0001811667752917856</v>
       </c>
       <c r="CY10" t="n">
-        <v>6.71848320052959e-05</v>
+        <v>0.0003458064456935972</v>
       </c>
       <c r="CZ10" t="n">
-        <v>5.49971082364209e-05</v>
+        <v>0.0001464842061977834</v>
       </c>
       <c r="DA10" t="n">
-        <v>4.860815170104615e-05</v>
+        <v>0.0001678225380601361</v>
       </c>
       <c r="DB10" t="n">
-        <v>6.131405825726688e-05</v>
+        <v>6.287213182076812e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.82713774847798e-05</v>
+        <v>1.854603851825232e-06</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.454955054214224e-06</v>
+        <v>0.0001886259560706094</v>
       </c>
       <c r="DE10" t="n">
-        <v>9.721504466142505e-05</v>
+        <v>0.0001947579730767757</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0002239989553345367</v>
+        <v>0.000257248873822391</v>
       </c>
       <c r="DG10" t="n">
-        <v>4.78887050121557e-05</v>
+        <v>0.0001425399677827954</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0002436225477140397</v>
+        <v>0.0001992198231164366</v>
       </c>
       <c r="DI10" t="n">
-        <v>2.269034848723095e-05</v>
+        <v>0.0001997100043809041</v>
       </c>
       <c r="DJ10" t="n">
-        <v>9.316961950389668e-06</v>
+        <v>0.0006097776349633932</v>
       </c>
       <c r="DK10" t="n">
-        <v>2.523056537029333e-05</v>
+        <v>0.000239280765526928</v>
       </c>
       <c r="DL10" t="n">
-        <v>6.175834278110415e-05</v>
+        <v>0.0007666020537726581</v>
       </c>
       <c r="DM10" t="n">
-        <v>3.016453410964459e-05</v>
+        <v>0.0001722723536659032</v>
       </c>
       <c r="DN10" t="n">
-        <v>7.193331111920998e-05</v>
+        <v>5.200181476539001e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>7.791955431457609e-05</v>
+        <v>0.0004446369712240994</v>
       </c>
       <c r="DP10" t="n">
-        <v>3.088244920945726e-05</v>
+        <v>6.154652510304004e-06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>4.365265704109333e-05</v>
+        <v>0.0002918518730439246</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.00012402911670506</v>
+        <v>0.0002686257648747414</v>
       </c>
       <c r="DS10" t="n">
-        <v>4.741940938401967e-05</v>
+        <v>0.0002944827429018915</v>
       </c>
       <c r="DT10" t="n">
-        <v>2.13382863876177e-05</v>
+        <v>0.0003014823596458882</v>
       </c>
       <c r="DU10" t="n">
-        <v>1.415470615029335e-05</v>
+        <v>0.0002539767592679709</v>
       </c>
       <c r="DV10" t="n">
-        <v>1.256005634786561e-05</v>
+        <v>0.0005194577388465405</v>
       </c>
       <c r="DW10" t="n">
-        <v>4.032808647025377e-06</v>
+        <v>0.0002098489640047774</v>
       </c>
       <c r="DX10" t="n">
-        <v>3.135056249448098e-05</v>
+        <v>0.0006271183374337852</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.447232878301293e-05</v>
+        <v>5.460049578687176e-05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.101681275235023e-06</v>
+        <v>8.092696953099221e-05</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0001246175088454038</v>
+        <v>0.0006291066529229283</v>
       </c>
       <c r="EB10" t="n">
-        <v>5.341026553651318e-05</v>
+        <v>0.0003051586973015219</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.943493043654598e-05</v>
+        <v>5.877324292669073e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>6.502070391434245e-06</v>
+        <v>0.0008985602180473506</v>
       </c>
       <c r="EE10" t="n">
-        <v>2.145686630683485e-05</v>
+        <v>0.000564845628105104</v>
       </c>
       <c r="EF10" t="n">
-        <v>2.038750244537368e-05</v>
+        <v>8.59821739140898e-05</v>
       </c>
       <c r="EG10" t="n">
-        <v>9.763566049514338e-05</v>
+        <v>0.0004951082519255579</v>
       </c>
       <c r="EH10" t="n">
-        <v>4.181356052868068e-05</v>
+        <v>3.425747854635119e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>1.944341238413472e-05</v>
+        <v>0.0002903806744143367</v>
       </c>
       <c r="EJ10" t="n">
-        <v>5.929839244345203e-05</v>
+        <v>0.0001372629922116175</v>
       </c>
       <c r="EK10" t="n">
-        <v>2.00560680241324e-05</v>
+        <v>0.0001968471333384514</v>
       </c>
       <c r="EL10" t="n">
-        <v>7.993593317223713e-05</v>
+        <v>6.957924779271707e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>2.258497625007294e-05</v>
+        <v>2.485793447704054e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>8.452588190266397e-06</v>
+        <v>0.0001137689177994616</v>
       </c>
       <c r="EO10" t="n">
-        <v>4.435816299519502e-05</v>
+        <v>5.895695358049124e-05</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0001554683258291334</v>
+        <v>0.0002916711382567883</v>
       </c>
       <c r="EQ10" t="n">
-        <v>2.862950714188628e-05</v>
+        <v>0.0001189436588902026</v>
       </c>
       <c r="ER10" t="n">
-        <v>6.575325096491724e-05</v>
+        <v>0.0003181979991495609</v>
       </c>
       <c r="ES10" t="n">
-        <v>9.720538946567103e-05</v>
+        <v>6.2233091739472e-05</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0001440073101548478</v>
+        <v>0.0001868212566478178</v>
       </c>
       <c r="EU10" t="n">
-        <v>9.010813664644957e-05</v>
+        <v>0.000135510548716411</v>
       </c>
       <c r="EV10" t="n">
-        <v>4.496745532378554e-05</v>
+        <v>7.919689232949167e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>3.121978807030246e-06</v>
+        <v>0.0002468620659783483</v>
       </c>
       <c r="EX10" t="n">
-        <v>4.050009465572657e-06</v>
+        <v>6.114496500231326e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0001595761714270338</v>
+        <v>0.0009415087988600135</v>
       </c>
       <c r="EZ10" t="n">
-        <v>2.285703158122487e-05</v>
+        <v>0.0001473867450840771</v>
       </c>
       <c r="FA10" t="n">
-        <v>6.382596620824188e-05</v>
+        <v>0.0003090126847382635</v>
       </c>
       <c r="FB10" t="n">
-        <v>5.007538129575551e-05</v>
+        <v>9.540516475681216e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>4.666752647608519e-05</v>
+        <v>0.0002026443107752129</v>
       </c>
       <c r="FD10" t="n">
-        <v>6.785131699871272e-05</v>
+        <v>4.357258876552805e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>2.738295734161511e-05</v>
+        <v>8.73366225278005e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>2.762617805274203e-05</v>
+        <v>0.0002222673647338524</v>
       </c>
       <c r="FG10" t="n">
-        <v>2.686364496184979e-06</v>
+        <v>0.0001810592802939937</v>
       </c>
       <c r="FH10" t="n">
-        <v>2.683207821974065e-05</v>
+        <v>0.0002660978352651</v>
       </c>
       <c r="FI10" t="n">
-        <v>2.637812758621294e-05</v>
+        <v>0.0003397014806978405</v>
       </c>
       <c r="FJ10" t="n">
-        <v>7.634596840944141e-05</v>
+        <v>0.0004341317981015891</v>
       </c>
       <c r="FK10" t="n">
-        <v>5.168620918993838e-05</v>
+        <v>3.057114736293443e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>3.959352761739865e-05</v>
+        <v>3.857939645968145e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>3.549728717189282e-05</v>
+        <v>0.0002079905825667083</v>
       </c>
       <c r="FN10" t="n">
-        <v>2.431657958368305e-05</v>
+        <v>0.0002035825164057314</v>
       </c>
       <c r="FO10" t="n">
-        <v>5.188507930142805e-05</v>
+        <v>0.000307616195641458</v>
       </c>
       <c r="FP10" t="n">
-        <v>5.720744957216084e-05</v>
+        <v>0.0001943034731084481</v>
       </c>
       <c r="FQ10" t="n">
-        <v>2.577585291874129e-05</v>
+        <v>0.0007579459925182164</v>
       </c>
       <c r="FR10" t="n">
-        <v>1.299885389016708e-05</v>
+        <v>2.020332613028586e-05</v>
       </c>
       <c r="FS10" t="n">
-        <v>4.739162250189111e-05</v>
+        <v>8.939045073930174e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0001480362116126344</v>
+        <v>0.000371241505490616</v>
       </c>
       <c r="FU10" t="n">
-        <v>1.770748713170178e-05</v>
+        <v>0.0002233974810224026</v>
       </c>
       <c r="FV10" t="n">
-        <v>3.98587180825416e-05</v>
+        <v>0.0001583360717631876</v>
       </c>
       <c r="FW10" t="n">
-        <v>8.14977684058249e-05</v>
+        <v>0.0001906556717585772</v>
       </c>
       <c r="FX10" t="n">
-        <v>6.742544064763933e-05</v>
+        <v>0.0003394073282834142</v>
       </c>
       <c r="FY10" t="n">
-        <v>6.614868470933288e-05</v>
+        <v>0.0001396948209730908</v>
       </c>
       <c r="FZ10" t="n">
-        <v>7.431953417835757e-05</v>
+        <v>0.0005377031629905105</v>
       </c>
       <c r="GA10" t="n">
-        <v>2.560486245783977e-05</v>
+        <v>5.620095180347562e-06</v>
       </c>
       <c r="GB10" t="n">
-        <v>2.136160765076056e-05</v>
+        <v>0.0001630764163564891</v>
       </c>
       <c r="GC10" t="n">
-        <v>9.000859427032992e-05</v>
+        <v>0.0003525862703099847</v>
       </c>
       <c r="GD10" t="n">
-        <v>8.166959742084146e-05</v>
+        <v>0.0002396398631390184</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0001980181114049628</v>
+        <v>0.0004553984617814422</v>
       </c>
       <c r="GF10" t="n">
-        <v>3.188385380781256e-05</v>
+        <v>0.0001965181872947142</v>
       </c>
       <c r="GG10" t="n">
-        <v>1.91324797924608e-05</v>
+        <v>7.815028948243707e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.002400087891146541</v>
+        <v>0.0008473568013869226</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02086326293647289</v>
+        <v>0.007397651672363281</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003328201593831182</v>
+        <v>0.001617157715372741</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00805305689573288</v>
+        <v>0.004633163101971149</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004949083551764488</v>
+        <v>0.000909921363927424</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004818160552531481</v>
+        <v>0.002239072928205132</v>
       </c>
       <c r="G11" t="n">
-        <v>3.637396730482578e-05</v>
+        <v>0.002310467883944511</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002533479128032923</v>
+        <v>0.001795547199435532</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00161838042549789</v>
+        <v>0.001109038013964891</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001080947462469339</v>
+        <v>0.0003049230435863137</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0171161126345396</v>
+        <v>0.007859583012759686</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001091355225071311</v>
+        <v>0.001839680597186089</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0108789075165987</v>
+        <v>0.006488909013569355</v>
       </c>
       <c r="N11" t="n">
-        <v>0.006624635774642229</v>
+        <v>0.002080548787489533</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00471777468919754</v>
+        <v>0.0007464416557922959</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0001456625759601593</v>
+        <v>0.001945276046171784</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.002048826310783625</v>
+        <v>0.0001515887852292508</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00305851292796433</v>
+        <v>0.000915748649276793</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004681008867919445</v>
+        <v>0.000387426174711436</v>
       </c>
       <c r="T11" t="n">
-        <v>0.004277513828128576</v>
+        <v>0.0009025245090015233</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001243097009137273</v>
+        <v>6.800964911235496e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001160738174803555</v>
+        <v>0.0004026429378427565</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0008821027586236596</v>
+        <v>0.0006780365947633982</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003646929515525699</v>
+        <v>0.001058869180269539</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00188277754932642</v>
+        <v>0.0003342887503094971</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0006042517488822341</v>
+        <v>0.0007502225344069302</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001292339293286204</v>
+        <v>0.001283479039557278</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.00256053963676095</v>
+        <v>0.0004082551749888808</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.003160098800435662</v>
+        <v>0.0001448167022317648</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0003527516091708094</v>
+        <v>0.0009105885401368141</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0007945683901198208</v>
+        <v>0.001625259639695287</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0002247653901576996</v>
+        <v>0.0004546780837699771</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00139406556263566</v>
+        <v>0.001517191645689309</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0008847899734973907</v>
+        <v>0.000614990247413516</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0006442695157602429</v>
+        <v>0.0002995331306010485</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0003706058487296104</v>
+        <v>0.000682300771586597</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.147026291117072e-06</v>
+        <v>0.0003615272580645978</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.003131942357867956</v>
+        <v>0.002320465631783009</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0003122077032458037</v>
+        <v>0.0007104811957105994</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0007233849610202014</v>
+        <v>0.001011452870443463</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001383369090035558</v>
+        <v>0.00172453944105655</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.002053335541859269</v>
+        <v>0.001045753830112517</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0005245800130069256</v>
+        <v>0.0002653941628523171</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.001496597891673446</v>
+        <v>0.0001889923587441444</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0007248935871757567</v>
+        <v>0.0003568710526451468</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.004686649423092604</v>
+        <v>0.0001215313823195174</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0132233863696456</v>
+        <v>0.004439043346792459</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0007649466278962791</v>
+        <v>0.0002497193054296076</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001792573602870107</v>
+        <v>0.001611517742276192</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0001979765074793249</v>
+        <v>0.003003878518939018</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0001865756639745086</v>
+        <v>0.0005785850225947797</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0004810412065126002</v>
+        <v>4.699740384239703e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0003668092540465295</v>
+        <v>0.0004646961460821331</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0002611672971397638</v>
+        <v>0.0004503779346123338</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0004391228721942753</v>
+        <v>0.0002463859273120761</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.003527452237904072</v>
+        <v>0.0002163034514524043</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.003490682225674391</v>
+        <v>0.001369216945022345</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.002280109561979771</v>
+        <v>0.0007612829795107245</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.008003660477697849</v>
+        <v>0.0003458349383436143</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.002492582891136408</v>
+        <v>0.0009759067324921489</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.002432436216622591</v>
+        <v>0.0005184635519981384</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.001004689838737249</v>
+        <v>0.0007492434233427048</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.002361099002882838</v>
+        <v>0.001369553268887103</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.00163504877127707</v>
+        <v>2.900023537222296e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.690443605184555e-05</v>
+        <v>0.0006472248351201415</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.00116668245755136</v>
+        <v>8.580465510021895e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0001076827466022223</v>
+        <v>0.000597802922129631</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0003238051722291857</v>
+        <v>4.039028135593981e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.002244824543595314</v>
+        <v>0.0001848027022788301</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0005279426695778966</v>
+        <v>0.0004278143169358373</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0004794353735633194</v>
+        <v>0.0001050233695423231</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0008119421545416117</v>
+        <v>0.0001066509721567854</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.002991957357153296</v>
+        <v>0.0005941913113929331</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.008101101033389568</v>
+        <v>0.003815341042354703</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002278680913150311</v>
+        <v>0.0003372763167135417</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.002854656893759966</v>
+        <v>0.001815462252125144</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.002580805215984583</v>
+        <v>0.0007201865082606673</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001575439353473485</v>
+        <v>0.0009464335162192583</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0005031974287703633</v>
+        <v>0.0006292325560934842</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0007414545980282128</v>
+        <v>0.0004090805887244642</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0007330332882702351</v>
+        <v>0.001037085661664605</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0001272474473807961</v>
+        <v>0.0002701599150896072</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.003448279108852148</v>
+        <v>0.00232292152941227</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0008288873941637576</v>
+        <v>0.000424717174610123</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.001126742106862366</v>
+        <v>0.001730076386593282</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0008398295613005757</v>
+        <v>0.0001065817050402984</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0009398341062478721</v>
+        <v>0.0004371055110823363</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0008049925090745091</v>
+        <v>2.72193574346602e-05</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0002681688347365707</v>
+        <v>0.0005317321047186852</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.000339919060934335</v>
+        <v>0.0002542531583458185</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.002686587395146489</v>
+        <v>0.0007340047159232199</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.001731200143694878</v>
+        <v>0.002370656235143542</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0003295050119049847</v>
+        <v>0.001289246138185263</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0003806061577051878</v>
+        <v>0.003099550027400255</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.002719829557463527</v>
+        <v>0.0008032890036702156</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.001640174654312432</v>
+        <v>0.000316959893098101</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0007140969391912222</v>
+        <v>0.001025660894811153</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.001977280247956514</v>
+        <v>0.000167098522069864</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0002963742590509355</v>
+        <v>0.0004688825865741819</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001539624645374715</v>
+        <v>9.489716467214748e-05</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.003037355840206146</v>
+        <v>0.002214704640209675</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.001077291439287364</v>
+        <v>0.0004017260507680476</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.001266861450858414</v>
+        <v>0.001751505536958575</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0004720918950624764</v>
+        <v>0.000180562594323419</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.001609801314771175</v>
+        <v>0.0004868797259405255</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0008137103286571801</v>
+        <v>9.837851393967867e-05</v>
       </c>
       <c r="DC11" t="n">
-        <v>8.924410212785006e-05</v>
+        <v>0.0005194467375986278</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.000212775485124439</v>
+        <v>0.000389674270991236</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0006846435717307031</v>
+        <v>0.0002190115337725729</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.005808839574456215</v>
+        <v>0.001755701727233827</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.001550544751808047</v>
+        <v>0.0007626536535099149</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.004400128033012152</v>
+        <v>0.001462031621485949</v>
       </c>
       <c r="DI11" t="n">
-        <v>5.282042548060417e-05</v>
+        <v>0.001514609321020544</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.002774310298264027</v>
+        <v>0.00211807107552886</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0002258592285215855</v>
+        <v>0.0002682466292753816</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0009777197847142816</v>
+        <v>0.002529630437493324</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0003026396443601698</v>
+        <v>0.0003939945599995553</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.000779853668063879</v>
+        <v>0.0001353702391497791</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.00106484058778733</v>
+        <v>0.001272097695618868</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001463065738789737</v>
+        <v>0.0004529666912276298</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0003838532138615847</v>
+        <v>0.0009153875871561468</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.003749038092792034</v>
+        <v>0.0003770123585127294</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.001087315031327307</v>
+        <v>0.0001240788988070562</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.001453126780688763</v>
+        <v>0.0009447101037949324</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0008839767542667687</v>
+        <v>0.000694358954206109</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0006881963345222175</v>
+        <v>0.001825021230615675</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0001931295410031453</v>
+        <v>0.0002825192932505161</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.002506338059902191</v>
+        <v>0.0002967201289720833</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0019553960300982</v>
+        <v>0.0007892536232247949</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.002371170790866017</v>
+        <v>0.0007221803534775972</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.001910612802021205</v>
+        <v>0.0002333930460736156</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.001904550706967711</v>
+        <v>0.001224853447638452</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0001832349662436172</v>
+        <v>0.0001830475666793063</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0007974555483087897</v>
+        <v>0.002475554356351495</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.00166037306189537</v>
+        <v>0.001998026855289936</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0003728047013282776</v>
+        <v>0.0001439115440007299</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.001776456483639777</v>
+        <v>0.001810857094824314</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0009981677867472172</v>
+        <v>0.0007265416788868606</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.001037450158037245</v>
+        <v>0.00146168633364141</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001143541885539889</v>
+        <v>0.0001834242721088231</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.002336017321795225</v>
+        <v>0.0004799047601409256</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0007045168895274401</v>
+        <v>1.086889824364334e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.000282625580439344</v>
+        <v>0.000675640651024878</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0002292058488819748</v>
+        <v>0.0001669910852797329</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0007903536316007376</v>
+        <v>0.0002808475110214204</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.001753928023390472</v>
+        <v>0.001888299360871315</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.001880203955806792</v>
+        <v>2.454208151903003e-05</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0004808463272638619</v>
+        <v>0.001248384127393365</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001139806816354394</v>
+        <v>0.000364420295227319</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.002904222579672933</v>
+        <v>0.0005852362373843789</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001025121076963842</v>
+        <v>0.0009001675061881542</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.001073656138032675</v>
+        <v>0.0006134447176009417</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0006036213599145412</v>
+        <v>0.0007082172087393701</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0005636093555949628</v>
+        <v>0.0002972220827359706</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.00330331502482295</v>
+        <v>0.002586058108136058</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.000257569452514872</v>
+        <v>0.0003789991023950279</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.001677283900789917</v>
+        <v>0.001997834537178278</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0007105080294422805</v>
+        <v>3.693873441079631e-05</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.001717699225991964</v>
+        <v>0.000560438318643719</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0009471625089645386</v>
+        <v>0.0002012695767916739</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0003401973517611623</v>
+        <v>0.0006717874784953892</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0002764560340438038</v>
+        <v>0.0004949592985212803</v>
       </c>
       <c r="FG11" t="n">
-        <v>2.688711174414493e-05</v>
+        <v>0.0004974006442353129</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.001518102013505995</v>
+        <v>0.001138477586209774</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0004308539791963995</v>
+        <v>0.0004188945167697966</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0006654099561274052</v>
+        <v>0.0006907368078827858</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.001382157555781305</v>
+        <v>0.0004314346297178417</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.001602979144081473</v>
+        <v>0.0003616813046392053</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0008968214970082045</v>
+        <v>0.0002084064035443589</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0003739538660738617</v>
+        <v>0.0003075001004617661</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0008960232953540981</v>
+        <v>0.001027564285323024</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.00367737072519958</v>
+        <v>0.0005014698253944516</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.006428077816963196</v>
+        <v>0.002341405022889376</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.001330853789113462</v>
+        <v>0.0006868717027828097</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.007716701366007328</v>
+        <v>0.0004969472647644579</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.002129078842699528</v>
+        <v>0.0002094182564178482</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.001033266540616751</v>
+        <v>0.0006287590367719531</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0007747760391794145</v>
+        <v>0.0006868224591016769</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0006563775241374969</v>
+        <v>0.0006330941105261445</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0006054958794265985</v>
+        <v>0.001020861673168838</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.002772375475615263</v>
+        <v>0.000853240373544395</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.001699402695521712</v>
+        <v>0.001750977942720056</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.000772693776525557</v>
+        <v>1.67149119079113e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0005276495357975364</v>
+        <v>0.001401585177518427</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.002483700634911656</v>
+        <v>0.001204177038744092</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0009473227546550333</v>
+        <v>0.0008447170839644969</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.003206765744835138</v>
+        <v>0.001304133096709847</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0001912977313622832</v>
+        <v>0.00101782800629735</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0001070374855771661</v>
+        <v>0.0002407015126664191</v>
       </c>
     </row>
     <row r="12">
@@ -7258,1140 +7258,1140 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6.365035369526595e-05</v>
+        <v>0.006959293037652969</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0009989474201574922</v>
+        <v>0.01757355593144894</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001663705479586497</v>
+        <v>0.001074359286576509</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003745494759641588</v>
+        <v>0.001521836500614882</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0008780342759564519</v>
+        <v>0.001491998322308064</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0004969699075445533</v>
+        <v>0.01513211708515882</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002746826212387532</v>
+        <v>0.004606732167303562</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005006091669201851</v>
+        <v>0.006357430014759302</v>
       </c>
       <c r="I13" t="n">
-        <v>1.194061951537151e-06</v>
+        <v>0.003825870342552662</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001359459420200437</v>
+        <v>0.006469901651144028</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0008383724489249289</v>
+        <v>0.02303441800177097</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001241407881025225</v>
+        <v>0.002435068599879742</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0001926469558384269</v>
+        <v>0.002364138374105096</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0008713589631952345</v>
+        <v>0.004600433632731438</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0006061723688617349</v>
+        <v>0.01461943611502647</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000155965011799708</v>
+        <v>0.001769141526892781</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.000119914322567638</v>
+        <v>0.0006957370787858963</v>
       </c>
       <c r="R13" t="n">
-        <v>4.649719994631596e-05</v>
+        <v>0.009424380026757717</v>
       </c>
       <c r="S13" t="n">
-        <v>6.355857476592064e-05</v>
+        <v>0.0006186654209159315</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0002645831555128098</v>
+        <v>0.00210696249268949</v>
       </c>
       <c r="U13" t="n">
-        <v>3.722603651112877e-05</v>
+        <v>0.002687686122953892</v>
       </c>
       <c r="V13" t="n">
-        <v>6.503421172965318e-05</v>
+        <v>0.003934625536203384</v>
       </c>
       <c r="W13" t="n">
-        <v>8.463764243060723e-05</v>
+        <v>0.003283256199210882</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0001543906109873205</v>
+        <v>0.002400879748165607</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.218872345518321e-05</v>
+        <v>0.0005291367415338755</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.372221105266362e-05</v>
+        <v>0.003835337003692985</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.968992526410148e-05</v>
+        <v>0.0004858567262999713</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.005231752060354e-06</v>
+        <v>0.001329101505689323</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0001010931664495729</v>
+        <v>0.002263708971440792</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001730940275592729</v>
+        <v>0.002195574343204498</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.377295070094988e-05</v>
+        <v>0.003011993831023574</v>
       </c>
       <c r="AF13" t="n">
-        <v>8.46692782943137e-05</v>
+        <v>0.005726009141653776</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0001510801957920194</v>
+        <v>0.00130374520085752</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0002820106165017933</v>
+        <v>0.0009736453648656607</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0001937994966283441</v>
+        <v>0.007992897182703018</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.167828304460272e-05</v>
+        <v>0.001456537283957005</v>
       </c>
       <c r="AK13" t="n">
-        <v>4.31941298302263e-05</v>
+        <v>0.001117238774895668</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0003432522353250533</v>
+        <v>0.003440659493207932</v>
       </c>
       <c r="AM13" t="n">
-        <v>6.024324466125108e-05</v>
+        <v>0.003667553421109915</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.633731492096558e-05</v>
+        <v>0.003558732103556395</v>
       </c>
       <c r="AO13" t="n">
-        <v>5.660275928676128e-05</v>
+        <v>0.0006402020226232708</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0001525242114439607</v>
+        <v>0.003134627360850573</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.253237446187995e-05</v>
+        <v>0.002134423237293959</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0001204665750265121</v>
+        <v>0.005152824800461531</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.56895640026778e-05</v>
+        <v>0.001429137540981174</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0001710369397187606</v>
+        <v>0.004385005682706833</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0007075258181430399</v>
+        <v>0.0184258446097374</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0001005754238576628</v>
+        <v>0.0032514538615942</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.067862780881114e-05</v>
+        <v>0.0006178658222779632</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.000140452990308404</v>
+        <v>0.001865156693384051</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0003402791917324066</v>
+        <v>0.009291841648519039</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.974190182518214e-05</v>
+        <v>0.0006780449766665697</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0002781597431749105</v>
+        <v>0.001533930655568838</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0001339044392807409</v>
+        <v>0.002303857356309891</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.776354035129771e-05</v>
+        <v>0.0009586147498339415</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0001386060903314501</v>
+        <v>3.990731784142554e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.097090302617289e-05</v>
+        <v>0.001537853968329728</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0002018740633502603</v>
+        <v>0.0002703340724110603</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0006341560510918498</v>
+        <v>0.001497202785685658</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.898652256699279e-05</v>
+        <v>0.004250046797096729</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0002540858404245228</v>
+        <v>0.00147438095882535</v>
       </c>
       <c r="BJ13" t="n">
-        <v>4.34178946306929e-05</v>
+        <v>0.003539612516760826</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.627351154340431e-05</v>
+        <v>0.001156599377281964</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001525406405562535</v>
+        <v>0.0003544387000147253</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.159835200174712e-05</v>
+        <v>0.004522990435361862</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.690447091590613e-05</v>
+        <v>0.0003379329282324761</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.701229484751821e-05</v>
+        <v>0.0006054116529412568</v>
       </c>
       <c r="BP13" t="n">
-        <v>8.903638808988035e-05</v>
+        <v>0.004898093640804291</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.000155583446030505</v>
+        <v>0.003153916215524077</v>
       </c>
       <c r="BR13" t="n">
-        <v>7.409441604977474e-05</v>
+        <v>0.006703528575599194</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.149954424472526e-05</v>
+        <v>1.03566053439863e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0001740085717756301</v>
+        <v>0.004127169027924538</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0001546811254229397</v>
+        <v>0.001249838969670236</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0004876434395555407</v>
+        <v>0.01160330604761839</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.000201822113012895</v>
+        <v>0.001514446106739342</v>
       </c>
       <c r="BX13" t="n">
-        <v>4.840746623813175e-05</v>
+        <v>0.004865453578531742</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0001380419125780463</v>
+        <v>5.006534047424793e-05</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7.048827683320269e-05</v>
+        <v>0.005541442893445492</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.284320751437917e-05</v>
+        <v>0.001476894016377628</v>
       </c>
       <c r="CB13" t="n">
-        <v>8.191652887035161e-05</v>
+        <v>0.0008302736678160727</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.660672180354595e-06</v>
+        <v>0.00194041000213474</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.101312045648228e-05</v>
+        <v>0.002947341650724411</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0001548003929201514</v>
+        <v>0.00542029645293951</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.246691221647779e-06</v>
+        <v>0.000746667617931962</v>
       </c>
       <c r="CG13" t="n">
-        <v>8.020149107323959e-05</v>
+        <v>0.001059540780261159</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0001140805470640771</v>
+        <v>0.00176269537769258</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0001272013760171831</v>
+        <v>0.003926323726773262</v>
       </c>
       <c r="CJ13" t="n">
-        <v>9.855190728558227e-05</v>
+        <v>0.002550861798226833</v>
       </c>
       <c r="CK13" t="n">
-        <v>5.516811870620586e-05</v>
+        <v>0.0009422157891094685</v>
       </c>
       <c r="CL13" t="n">
-        <v>4.094188625458628e-06</v>
+        <v>0.0003540181496646255</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0001125091293943115</v>
+        <v>0.0001917602494359016</v>
       </c>
       <c r="CN13" t="n">
-        <v>6.428410415537655e-06</v>
+        <v>0.008975743316113949</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.511960908828769e-05</v>
+        <v>0.002162681892514229</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.323319858987816e-05</v>
+        <v>0.003615995636209846</v>
       </c>
       <c r="CQ13" t="n">
-        <v>7.022760655672755e-06</v>
+        <v>0.004934325348585844</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.864454861788545e-05</v>
+        <v>0.002822019392624497</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0002995783870574087</v>
+        <v>0.001402133144438267</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0002612328389659524</v>
+        <v>0.0004143238766118884</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.115133454732131e-05</v>
+        <v>0.0004747812636196613</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.112804213538766e-05</v>
+        <v>0.001789002097211778</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0001074285537470132</v>
+        <v>0.004848549142479897</v>
       </c>
       <c r="CX13" t="n">
-        <v>2.920085353252944e-05</v>
+        <v>0.0004983928520232439</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0001046092438627966</v>
+        <v>0.0005867959698662162</v>
       </c>
       <c r="CZ13" t="n">
-        <v>8.155334944603965e-05</v>
+        <v>0.001712893019430339</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0001670978090260178</v>
+        <v>0.003814264433458447</v>
       </c>
       <c r="DB13" t="n">
-        <v>6.633448356296867e-05</v>
+        <v>0.0009243020322173834</v>
       </c>
       <c r="DC13" t="n">
-        <v>4.096170232514851e-05</v>
+        <v>0.001529229688458145</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.065093162353151e-05</v>
+        <v>0.0005771203432232141</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001467741967644542</v>
+        <v>0.0009469446958974004</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0002130674693034962</v>
+        <v>0.005997514352202415</v>
       </c>
       <c r="DG13" t="n">
-        <v>4.978289871360175e-05</v>
+        <v>0.003141081193462014</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0002646515786182135</v>
+        <v>0.001411327044479549</v>
       </c>
       <c r="DI13" t="n">
-        <v>5.277543095871806e-05</v>
+        <v>0.005162879358977079</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0001246624015038833</v>
+        <v>0.003630803199484944</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.000195121974684298</v>
+        <v>0.0004817071603611112</v>
       </c>
       <c r="DL13" t="n">
-        <v>2.720341944950633e-05</v>
+        <v>0.004347239620983601</v>
       </c>
       <c r="DM13" t="n">
-        <v>7.20583375368733e-06</v>
+        <v>0.0006404111627489328</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.566429273225367e-05</v>
+        <v>0.002115380251780152</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.924602788174525e-05</v>
+        <v>0.002709389198571444</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0001043174852384254</v>
+        <v>0.002082532038912177</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0002997980336658657</v>
+        <v>0.003759092185646296</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.972292223712429e-05</v>
+        <v>0.0004738972056657076</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0003360790433362126</v>
+        <v>0.00373682496137917</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0001050753417075612</v>
+        <v>0.000704483943991363</v>
       </c>
       <c r="DU13" t="n">
-        <v>8.907616575015709e-06</v>
+        <v>0.004305510316044092</v>
       </c>
       <c r="DV13" t="n">
-        <v>6.9841044023633e-06</v>
+        <v>0.001641087350435555</v>
       </c>
       <c r="DW13" t="n">
-        <v>5.849201261298731e-05</v>
+        <v>0.003053779248148203</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.597815733286552e-07</v>
+        <v>0.001951229758560658</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0001074261163012125</v>
+        <v>0.001581161515787244</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0001100930094253272</v>
+        <v>0.001671707141213119</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0001266184990527108</v>
+        <v>0.0005346964462660253</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0002252018311992288</v>
+        <v>0.003730323631316423</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0001334302505711094</v>
+        <v>0.0004443112411536276</v>
       </c>
       <c r="ED13" t="n">
-        <v>3.955505235353485e-05</v>
+        <v>0.002926432993263006</v>
       </c>
       <c r="EE13" t="n">
-        <v>1.123236870625988e-06</v>
+        <v>0.006257654167711735</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0001143964618677273</v>
+        <v>0.002843213966116309</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0001366972719551995</v>
+        <v>0.0001095399493351579</v>
       </c>
       <c r="EH13" t="n">
-        <v>2.618363760120701e-05</v>
+        <v>0.002474985318258405</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0001204645959660411</v>
+        <v>0.0001741215237416327</v>
       </c>
       <c r="EJ13" t="n">
-        <v>9.969400707632303e-05</v>
+        <v>0.003493398427963257</v>
       </c>
       <c r="EK13" t="n">
-        <v>8.376905498153064e-06</v>
+        <v>0.002050825860351324</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001136694045271724</v>
+        <v>0.001307285157963634</v>
       </c>
       <c r="EM13" t="n">
-        <v>1.239776975126006e-05</v>
+        <v>5.484958091983572e-05</v>
       </c>
       <c r="EN13" t="n">
-        <v>4.343495675129816e-05</v>
+        <v>0.0005182201857678592</v>
       </c>
       <c r="EO13" t="n">
-        <v>1.144745692727156e-05</v>
+        <v>0.002211126266047359</v>
       </c>
       <c r="EP13" t="n">
-        <v>6.752795889042318e-05</v>
+        <v>0.002299670595675707</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0001698376581771299</v>
+        <v>0.0004076549084857106</v>
       </c>
       <c r="ER13" t="n">
-        <v>9.237072663381696e-05</v>
+        <v>0.002061181468889117</v>
       </c>
       <c r="ES13" t="n">
-        <v>8.683495252626017e-06</v>
+        <v>0.005842088721692562</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0002380037331022322</v>
+        <v>0.004423084668815136</v>
       </c>
       <c r="EU13" t="n">
-        <v>2.547447729739361e-05</v>
+        <v>0.0004685128224082291</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0001090509686036967</v>
+        <v>0.000840946042444557</v>
       </c>
       <c r="EW13" t="n">
-        <v>2.446310099912807e-05</v>
+        <v>0.002145136008039117</v>
       </c>
       <c r="EX13" t="n">
-        <v>4.281318979337811e-06</v>
+        <v>0.002600685460492969</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0001048463527695276</v>
+        <v>0.006314358208328485</v>
       </c>
       <c r="EZ13" t="n">
-        <v>1.27439043353661e-05</v>
+        <v>0.0004249331541359425</v>
       </c>
       <c r="FA13" t="n">
-        <v>9.777642117114738e-05</v>
+        <v>0.0004824253264814615</v>
       </c>
       <c r="FB13" t="n">
-        <v>7.65781951486133e-05</v>
+        <v>0.002825268544256687</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0001473045849706978</v>
+        <v>0.003364841220900416</v>
       </c>
       <c r="FD13" t="n">
-        <v>9.587097156327218e-05</v>
+        <v>0.002264435170218349</v>
       </c>
       <c r="FE13" t="n">
-        <v>5.983915616525337e-05</v>
+        <v>0.001145262620411813</v>
       </c>
       <c r="FF13" t="n">
-        <v>5.285808583721519e-06</v>
+        <v>0.0008209331426769495</v>
       </c>
       <c r="FG13" t="n">
-        <v>3.638419366325252e-05</v>
+        <v>0.0008108459296636283</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0001824507780838758</v>
+        <v>0.005985331255942583</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.000113660455099307</v>
+        <v>0.003373383078724146</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0001952498423634097</v>
+        <v>0.002071229275316</v>
       </c>
       <c r="FK13" t="n">
-        <v>4.032172000734136e-05</v>
+        <v>0.001683504087850451</v>
       </c>
       <c r="FL13" t="n">
-        <v>4.008363976026885e-05</v>
+        <v>0.00554252602159977</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0001100383378798142</v>
+        <v>0.002221977105364203</v>
       </c>
       <c r="FN13" t="n">
-        <v>1.723636887618341e-05</v>
+        <v>0.006834711413830519</v>
       </c>
       <c r="FO13" t="n">
-        <v>9.928636427503079e-05</v>
+        <v>0.004988400265574455</v>
       </c>
       <c r="FP13" t="n">
-        <v>2.884686909965239e-05</v>
+        <v>0.002068178728222847</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0002627001667860895</v>
+        <v>0.003105847164988518</v>
       </c>
       <c r="FR13" t="n">
-        <v>2.977995973196812e-05</v>
+        <v>0.008406059816479683</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0001819324970711023</v>
+        <v>0.004030095413327217</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0002069782931357622</v>
+        <v>0.001290767686441541</v>
       </c>
       <c r="FU13" t="n">
-        <v>1.791231625247747e-05</v>
+        <v>0.001363128423690796</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0001306483754888177</v>
+        <v>5.862675607204437e-05</v>
       </c>
       <c r="FW13" t="n">
-        <v>2.175753616029397e-05</v>
+        <v>0.003399956738576293</v>
       </c>
       <c r="FX13" t="n">
-        <v>1.487522968091071e-05</v>
+        <v>0.001850885804742575</v>
       </c>
       <c r="FY13" t="n">
-        <v>1.238673576153815e-06</v>
+        <v>0.003729830030351877</v>
       </c>
       <c r="FZ13" t="n">
-        <v>4.507887297222624e-06</v>
+        <v>0.001333741238340735</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.000256900122622028</v>
+        <v>0.002255052560940385</v>
       </c>
       <c r="GB13" t="n">
-        <v>6.266440323088318e-05</v>
+        <v>0.001388344564475119</v>
       </c>
       <c r="GC13" t="n">
-        <v>5.579938078881241e-05</v>
+        <v>0.004330083262175322</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0002060320548480377</v>
+        <v>0.004516278393566608</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0002857010695151985</v>
+        <v>0.0002135468239430338</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0001512705493951216</v>
+        <v>0.002991367131471634</v>
       </c>
       <c r="GG13" t="n">
-        <v>2.839876106008887e-05</v>
+        <v>0.00496404618024826</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.000125910431961529</v>
+        <v>2.206550359096227e-10</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001272230758331716</v>
+        <v>1.367725155354549e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001609665923751891</v>
+        <v>2.047870067967139e-10</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004192398919258267</v>
+        <v>8.778978655143987e-10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001462477608583868</v>
+        <v>1.117599124356161e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003685933188535273</v>
+        <v>1.939943761186669e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001431512355338782</v>
+        <v>2.477453242555328e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00033618847373873</v>
+        <v>7.262613843650456e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>9.579286415828392e-05</v>
+        <v>1.234836538577255e-11</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002877461956813931</v>
+        <v>2.312500468892864e-10</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001148673356510699</v>
+        <v>1.195538001930174e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002825409173965454</v>
+        <v>6.619734205237648e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0001138535953941755</v>
+        <v>4.635488104476337e-10</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001268102088943124</v>
+        <v>2.447788916004612e-10</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0005276579759083688</v>
+        <v>2.202398263762007e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001036816975101829</v>
+        <v>2.693302872391889e-11</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.074256528634578e-05</v>
+        <v>9.23112364326073e-10</v>
       </c>
       <c r="R14" t="n">
-        <v>1.242564212589059e-05</v>
+        <v>4.966580618992467e-11</v>
       </c>
       <c r="S14" t="n">
-        <v>5.848981891176663e-05</v>
+        <v>3.064132836350097e-10</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0003215434844605625</v>
+        <v>3.095005085551605e-10</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001430762786185369</v>
+        <v>1.735657451096273e-10</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0001993664773181081</v>
+        <v>2.03293687439654e-10</v>
       </c>
       <c r="W14" t="n">
-        <v>2.05215546884574e-05</v>
+        <v>2.005309113206621e-10</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0002755048626568168</v>
+        <v>7.563852322256537e-10</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.603657675441355e-05</v>
+        <v>3.639082091222434e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.982984632486477e-05</v>
+        <v>8.447944011003017e-10</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.179880776675418e-05</v>
+        <v>2.22060078658437e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.487635356374085e-05</v>
+        <v>5.341520559198898e-10</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0001214834774145856</v>
+        <v>9.270442746789342e-10</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0002829593140631914</v>
+        <v>4.638884276708666e-10</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.452510852890555e-05</v>
+        <v>1.634309909626097e-10</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.010650395182893e-05</v>
+        <v>2.786166297674697e-10</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0002184914628742263</v>
+        <v>1.321579512492121e-10</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0002642495092004538</v>
+        <v>1.418169470746022e-10</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0003367685130797327</v>
+        <v>5.56908200111117e-11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6.447939085774124e-05</v>
+        <v>1.684500455789717e-10</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.845276271225885e-05</v>
+        <v>1.74928377338901e-10</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0004561593814287335</v>
+        <v>4.012710996814661e-10</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0001712326484266669</v>
+        <v>2.620708372536029e-10</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.738513674354181e-05</v>
+        <v>7.013107455877687e-11</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.379141122015426e-05</v>
+        <v>1.180739533923614e-11</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0001074639149010181</v>
+        <v>1.479025790729338e-10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.922104512341321e-05</v>
+        <v>3.112182733744362e-10</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0001073121748049743</v>
+        <v>5.956733023504412e-11</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.000133438064949587</v>
+        <v>5.183138918063435e-10</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0002732630528043956</v>
+        <v>3.477408361263201e-10</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001097593572922051</v>
+        <v>8.200167767036248e-10</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.017580234474735e-05</v>
+        <v>5.943227021631969e-10</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.16994555760175e-05</v>
+        <v>1.998769483257945e-10</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0001771941606421024</v>
+        <v>7.900614606981549e-10</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.274372132495046e-07</v>
+        <v>2.392090692193705e-10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.000146271864650771</v>
+        <v>6.073853919819072e-11</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0003647804551292211</v>
+        <v>4.525703145574766e-10</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0003186691028531641</v>
+        <v>6.047086720251116e-10</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.289595744921826e-05</v>
+        <v>2.338816085245554e-10</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.602257129386999e-05</v>
+        <v>1.369829139008516e-09</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.969839260913432e-05</v>
+        <v>8.658279648798839e-11</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.000238589127548039</v>
+        <v>6.036865451974904e-10</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0009752990445122123</v>
+        <v>2.182845459941518e-09</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.000350321177393198</v>
+        <v>5.589301244057765e-10</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0002817967033479363</v>
+        <v>3.493079991923054e-10</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0001506345288362354</v>
+        <v>7.585247985275601e-10</v>
       </c>
       <c r="BK14" t="n">
-        <v>9.809286711970344e-05</v>
+        <v>7.264473467216703e-10</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001759847509674728</v>
+        <v>1.855581660548111e-10</v>
       </c>
       <c r="BM14" t="n">
-        <v>4.480569259612821e-05</v>
+        <v>4.018895771729092e-10</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.374476338853128e-05</v>
+        <v>9.381904975125366e-11</v>
       </c>
       <c r="BO14" t="n">
-        <v>7.420685869874433e-05</v>
+        <v>2.041025959353959e-10</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.233517054468393e-05</v>
+        <v>5.622721177545031e-10</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0002686497173272073</v>
+        <v>2.410108917993981e-11</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.00011667818762362</v>
+        <v>2.022367828757865e-10</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.066588083631359e-05</v>
+        <v>2.33038366381777e-10</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0002006922732107341</v>
+        <v>1.388755638265238e-10</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0002253083075629547</v>
+        <v>2.269306131896798e-10</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0007179504609666765</v>
+        <v>4.306330847470008e-10</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0002300613996339962</v>
+        <v>2.521043651615429e-10</v>
       </c>
       <c r="BX14" t="n">
-        <v>1.506642365711741e-05</v>
+        <v>3.383156949032795e-11</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.084283525822684e-05</v>
+        <v>1.81636216484149e-12</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0001961136149475351</v>
+        <v>8.874403434333544e-10</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.746909588808194e-05</v>
+        <v>2.373297114388606e-10</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.000129871943499893</v>
+        <v>2.774382112935569e-10</v>
       </c>
       <c r="CC14" t="n">
-        <v>8.229797094827518e-05</v>
+        <v>4.688859855939143e-10</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.053775097010657e-05</v>
+        <v>1.399712984406776e-10</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0002163777244277298</v>
+        <v>3.676473014913029e-11</v>
       </c>
       <c r="CF14" t="n">
-        <v>5.364677053876221e-05</v>
+        <v>2.997541798110959e-11</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0001154562633018941</v>
+        <v>7.268093765722128e-11</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001786318025551736</v>
+        <v>4.337185888214634e-10</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0001199882754008286</v>
+        <v>5.99587990368633e-10</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.000159548842930235</v>
+        <v>6.755819514925321e-11</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.320613228017464e-05</v>
+        <v>1.639546276521742e-10</v>
       </c>
       <c r="CL14" t="n">
-        <v>4.050535790156573e-05</v>
+        <v>8.733186396270298e-11</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0001657019311096519</v>
+        <v>9.869849382226903e-11</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0001070839498424903</v>
+        <v>8.668432638359036e-10</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.13820196929737e-05</v>
+        <v>4.648095797143981e-10</v>
       </c>
       <c r="CP14" t="n">
-        <v>3.638229827629402e-06</v>
+        <v>1.48212345174592e-10</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0001965808478416875</v>
+        <v>9.838676540141478e-10</v>
       </c>
       <c r="CR14" t="n">
-        <v>5.007392246625386e-05</v>
+        <v>5.181567397372078e-10</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0002969976339954883</v>
+        <v>2.549669364526608e-10</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0002377029450144619</v>
+        <v>8.095984993516936e-11</v>
       </c>
       <c r="CU14" t="n">
-        <v>9.194097947329283e-05</v>
+        <v>3.395548842100027e-10</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.242711732629687e-06</v>
+        <v>1.135713953437367e-10</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0001569041633047163</v>
+        <v>1.465859655880308e-10</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.269961467187386e-05</v>
+        <v>9.945762963203819e-12</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0001370622630929574</v>
+        <v>7.518535793948899e-11</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0001526195701444522</v>
+        <v>2.156230194394482e-10</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0001963496615644544</v>
+        <v>6.357018245140011e-10</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001269711356144398</v>
+        <v>2.398700960082323e-10</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.526434061815962e-05</v>
+        <v>2.295703627197554e-10</v>
       </c>
       <c r="DD14" t="n">
-        <v>8.59260544530116e-05</v>
+        <v>1.693824663862031e-10</v>
       </c>
       <c r="DE14" t="n">
-        <v>7.846286462154239e-05</v>
+        <v>1.997277343512849e-11</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0002946341701317579</v>
+        <v>1.707905372683172e-09</v>
       </c>
       <c r="DG14" t="n">
-        <v>8.612021338194609e-05</v>
+        <v>4.224771366079239e-10</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0003664848918560892</v>
+        <v>3.22527005103268e-10</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0002613588003441691</v>
+        <v>5.663915447762236e-10</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.843439506250434e-05</v>
+        <v>4.784674323410343e-10</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.000223042254219763</v>
+        <v>6.849197320413225e-10</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0001954612816916779</v>
+        <v>3.894873312759728e-10</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0001680410641711205</v>
+        <v>2.631792006546618e-10</v>
       </c>
       <c r="DN14" t="n">
-        <v>4.186763544566929e-05</v>
+        <v>4.787025220664987e-10</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.281509478052612e-05</v>
+        <v>3.320492214520243e-10</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.023817983688787e-05</v>
+        <v>1.862224541238078e-10</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0003753488999791443</v>
+        <v>9.001384082552022e-10</v>
       </c>
       <c r="DR14" t="n">
-        <v>4.768848157254979e-05</v>
+        <v>1.173648678243211e-11</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0005644774064421654</v>
+        <v>7.160161352715022e-11</v>
       </c>
       <c r="DT14" t="n">
-        <v>6.176367605803534e-05</v>
+        <v>1.056087578499287e-10</v>
       </c>
       <c r="DU14" t="n">
-        <v>5.757037433795631e-05</v>
+        <v>2.60377858163352e-10</v>
       </c>
       <c r="DV14" t="n">
-        <v>5.148552736500278e-05</v>
+        <v>3.782236746019407e-10</v>
       </c>
       <c r="DW14" t="n">
-        <v>1.317620990448631e-05</v>
+        <v>3.476322563145118e-10</v>
       </c>
       <c r="DX14" t="n">
-        <v>1.031744614010677e-05</v>
+        <v>6.193352497518845e-10</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.112820170121267e-05</v>
+        <v>5.445019990446553e-10</v>
       </c>
       <c r="DZ14" t="n">
-        <v>8.083781722234562e-05</v>
+        <v>6.448200862152476e-10</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0001345797791145742</v>
+        <v>1.476609612360846e-09</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.000335894146701321</v>
+        <v>5.639280709068828e-10</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0001460866333218291</v>
+        <v>1.788307280037316e-10</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0001494263560744002</v>
+        <v>8.122486017114738e-10</v>
       </c>
       <c r="EE14" t="n">
-        <v>3.376327367732301e-05</v>
+        <v>2.818494604373001e-10</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.000136756629217416</v>
+        <v>2.021023765008678e-10</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0001873921864898875</v>
+        <v>5.296197924664625e-10</v>
       </c>
       <c r="EH14" t="n">
-        <v>8.463902304356452e-06</v>
+        <v>3.761092548515421e-10</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001434573059668764</v>
+        <v>9.119416888303533e-10</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0002169950021198019</v>
+        <v>2.043403640739072e-10</v>
       </c>
       <c r="EK14" t="n">
-        <v>2.39320652326569e-05</v>
+        <v>6.513656836126813e-10</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001439248881069943</v>
+        <v>4.505469261562034e-11</v>
       </c>
       <c r="EM14" t="n">
-        <v>8.362170774489641e-06</v>
+        <v>3.515221447258909e-10</v>
       </c>
       <c r="EN14" t="n">
-        <v>9.829021291807294e-05</v>
+        <v>1.668500754226088e-10</v>
       </c>
       <c r="EO14" t="n">
-        <v>5.917712041991763e-05</v>
+        <v>4.132393732758644e-11</v>
       </c>
       <c r="EP14" t="n">
-        <v>3.589883999666199e-05</v>
+        <v>9.524575572683602e-11</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001476000907132402</v>
+        <v>2.962055600796987e-10</v>
       </c>
       <c r="ER14" t="n">
-        <v>8.142797014443204e-06</v>
+        <v>1.378268610352507e-10</v>
       </c>
       <c r="ES14" t="n">
-        <v>6.154867151053622e-05</v>
+        <v>3.483416888272473e-10</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.000283614790532738</v>
+        <v>2.362813278367071e-10</v>
       </c>
       <c r="EU14" t="n">
-        <v>5.311657878337428e-05</v>
+        <v>1.348021139158107e-10</v>
       </c>
       <c r="EV14" t="n">
-        <v>9.353778295917436e-05</v>
+        <v>6.066044888619615e-10</v>
       </c>
       <c r="EW14" t="n">
-        <v>7.968770660227165e-06</v>
+        <v>3.05435537972798e-11</v>
       </c>
       <c r="EX14" t="n">
-        <v>2.667877924977802e-05</v>
+        <v>2.183754288509476e-10</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0001646681193960831</v>
+        <v>1.960697576519621e-10</v>
       </c>
       <c r="EZ14" t="n">
-        <v>4.745188562083058e-05</v>
+        <v>7.12002262703848e-11</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0001213126670336351</v>
+        <v>2.866271109347451e-11</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0001297581184189767</v>
+        <v>4.382328944174674e-10</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0001784527557902038</v>
+        <v>6.413095055002316e-10</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001259007840417325</v>
+        <v>1.001596305894026e-10</v>
       </c>
       <c r="FE14" t="n">
-        <v>1.404376234859228e-05</v>
+        <v>3.279175264658818e-10</v>
       </c>
       <c r="FF14" t="n">
-        <v>2.461344411130995e-05</v>
+        <v>1.874626148756775e-11</v>
       </c>
       <c r="FG14" t="n">
-        <v>9.623727237340063e-05</v>
+        <v>1.187824838488893e-11</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0001415610313415527</v>
+        <v>3.303676776589271e-10</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0001645202282816172</v>
+        <v>7.844439542381565e-10</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0002624462358653545</v>
+        <v>7.557778292088813e-10</v>
       </c>
       <c r="FK14" t="n">
-        <v>4.245624950272031e-06</v>
+        <v>8.776849247382756e-10</v>
       </c>
       <c r="FL14" t="n">
-        <v>2.823724571499042e-05</v>
+        <v>3.930737957347219e-10</v>
       </c>
       <c r="FM14" t="n">
-        <v>8.804276149021462e-06</v>
+        <v>1.135960353559895e-10</v>
       </c>
       <c r="FN14" t="n">
-        <v>7.652553904335946e-06</v>
+        <v>7.123097667260936e-10</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0001079555950127542</v>
+        <v>1.816056055536919e-10</v>
       </c>
       <c r="FP14" t="n">
-        <v>1.39057265187148e-05</v>
+        <v>8.564819964362869e-10</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0004558544897008687</v>
+        <v>8.55981063807576e-10</v>
       </c>
       <c r="FR14" t="n">
-        <v>5.70367556065321e-05</v>
+        <v>1.586892617311264e-09</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0001488922425778583</v>
+        <v>5.630846344750751e-10</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001432624849257991</v>
+        <v>9.67896651715705e-10</v>
       </c>
       <c r="FU14" t="n">
-        <v>8.603688911534846e-05</v>
+        <v>5.549503079294027e-10</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001056782057275996</v>
+        <v>1.344958588944678e-09</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0002135794929927215</v>
+        <v>1.04199482375833e-10</v>
       </c>
       <c r="FX14" t="n">
-        <v>2.137193223461509e-05</v>
+        <v>1.165561397398207e-10</v>
       </c>
       <c r="FY14" t="n">
-        <v>2.070839400403202e-05</v>
+        <v>4.286052901480986e-10</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0001869805564638227</v>
+        <v>1.978606167796215e-11</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0002480068651493639</v>
+        <v>5.038905959153794e-10</v>
       </c>
       <c r="GB14" t="n">
-        <v>5.0194954383187e-05</v>
+        <v>6.150503439883437e-10</v>
       </c>
       <c r="GC14" t="n">
-        <v>8.982249710243195e-06</v>
+        <v>7.475088881214731e-10</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0002271884877700359</v>
+        <v>6.913194461333205e-10</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0002260485198348761</v>
+        <v>2.012471092549539e-11</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001710909564280882</v>
+        <v>5.563592642143789e-11</v>
       </c>
       <c r="GG14" t="n">
-        <v>1.172891643363982e-06</v>
+        <v>2.948402633151659e-10</v>
       </c>
     </row>
     <row r="15">
@@ -8965,571 +8965,571 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0007514450699090958</v>
+        <v>2.075531256195973e-06</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002360528567805886</v>
+        <v>4.65115863335086e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0006246225093491375</v>
+        <v>5.375922000894207e-07</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005634762346744537</v>
+        <v>1.152083768829471e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001089205383323133</v>
+        <v>9.816012607188895e-07</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002182751893997192</v>
+        <v>1.464041588405962e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0003292417386546731</v>
+        <v>5.816668817715254e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0004917393089272082</v>
+        <v>8.425141686529969e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001404701470164582</v>
+        <v>3.125111334156827e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0004903624067083001</v>
+        <v>1.525295033388829e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001614714507013559</v>
+        <v>4.987468400940998e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003040237061213702</v>
+        <v>4.591981905832654e-07</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0003041207673959434</v>
+        <v>1.671047016316152e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001104046474210918</v>
+        <v>2.218338295278954e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>0.002304403111338615</v>
+        <v>2.105347221004195e-06</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0004298030398786068</v>
+        <v>1.490454479835535e-07</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0002689454704523087</v>
+        <v>4.813864507013932e-08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.388367309118621e-05</v>
+        <v>1.266555500478717e-06</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0002602388267405331</v>
+        <v>6.761378585906641e-07</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0004268890479579568</v>
+        <v>3.385944467027002e-07</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0002219926100224257</v>
+        <v>4.405623315051344e-07</v>
       </c>
       <c r="V16" t="n">
-        <v>0.000309052353259176</v>
+        <v>6.40153359654505e-07</v>
       </c>
       <c r="W16" t="n">
-        <v>0.001056633191183209</v>
+        <v>9.005802894535009e-07</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0001034821616485715</v>
+        <v>6.372912366714445e-07</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0006342313718050718</v>
+        <v>6.548252144966682e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0002543039154261351</v>
+        <v>7.9780289752307e-07</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0002508324978407472</v>
+        <v>2.302830495182207e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0004327317874412984</v>
+        <v>2.44158172790776e-07</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0008592366357333958</v>
+        <v>3.767864882320282e-07</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0006841417634859681</v>
+        <v>4.289500452614448e-07</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0007365352939814329</v>
+        <v>1.668326262915798e-06</v>
       </c>
       <c r="AF16" t="n">
-        <v>4.970601003151387e-05</v>
+        <v>1.747936266838224e-06</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0004774128319695592</v>
+        <v>5.496177095665189e-07</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0001386887452099472</v>
+        <v>6.656230766566296e-07</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0005805112887173891</v>
+        <v>1.357022711090394e-06</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.496583692845888e-05</v>
+        <v>4.842692078455002e-07</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0006773836212232709</v>
+        <v>9.454872156311467e-07</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0001438232720829546</v>
+        <v>5.282064989842183e-07</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.650342503329739e-05</v>
+        <v>4.901995680484106e-07</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0001608142192708328</v>
+        <v>1.112395239033503e-06</v>
       </c>
       <c r="AO16" t="n">
-        <v>8.953809447120875e-05</v>
+        <v>2.043657332251314e-08</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0001198830723296851</v>
+        <v>5.083630298940989e-07</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.735430699540302e-05</v>
+        <v>6.052624712538091e-07</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0004716043185908347</v>
+        <v>2.842398316715844e-07</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0001005502927000634</v>
+        <v>2.392291378328082e-07</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.903707541525364e-05</v>
+        <v>1.512627250122023e-06</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.002159163122996688</v>
+        <v>3.078472445849911e-06</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0002326926041860133</v>
+        <v>1.433570560038788e-07</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.001538637327030301</v>
+        <v>7.331608458116534e-07</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0002979513083118945</v>
+        <v>2.324616161786253e-06</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0006434664828702807</v>
+        <v>1.399581606165157e-06</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0009126143413595855</v>
+        <v>2.343972056451094e-07</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0002975556999444962</v>
+        <v>9.480025369157374e-07</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0001016243259073235</v>
+        <v>3.996704549535934e-07</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.501204916276038e-05</v>
+        <v>1.200714223159594e-06</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0004506955738179386</v>
+        <v>1.137192271016829e-06</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0007539672660641372</v>
+        <v>8.585170121477859e-07</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0005752503057010472</v>
+        <v>1.936438422944775e-07</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0007788049406372011</v>
+        <v>1.118213617701258e-06</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.001120250206440687</v>
+        <v>6.790348834329052e-07</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0001692330843070522</v>
+        <v>6.389741429302376e-07</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.0004489238781388849</v>
+        <v>5.919638397244853e-07</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.0001228094333782792</v>
+        <v>1.645687461859779e-07</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0003280390228610486</v>
+        <v>2.51688732078037e-07</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0003565545775927603</v>
+        <v>3.399411525606411e-07</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0001273289090022445</v>
+        <v>2.867480475288176e-07</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.0002629705704748631</v>
+        <v>2.863048962353787e-07</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0003326736332383007</v>
+        <v>6.340528670989443e-07</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.0001258221891475841</v>
+        <v>8.037059728849272e-08</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0001571472821524367</v>
+        <v>8.894359666555829e-07</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0001376250147586688</v>
+        <v>3.600693503358343e-07</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0001994588819798082</v>
+        <v>7.535725217167055e-07</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.0003588999679777771</v>
+        <v>1.974194447029731e-06</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0006887818453833461</v>
+        <v>1.651127263357921e-06</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0004150649183429778</v>
+        <v>2.104247442957785e-07</v>
       </c>
       <c r="BX16" t="n">
-        <v>9.170055272988975e-05</v>
+        <v>4.405680442687299e-07</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0001054466192726977</v>
+        <v>4.726314273284515e-07</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0002678096643649042</v>
+        <v>1.276042326026072e-06</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.0001815774012356997</v>
+        <v>8.175145467248512e-07</v>
       </c>
       <c r="CB16" t="n">
-        <v>7.601050310768187e-05</v>
+        <v>1.922727506098454e-07</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0003058089932892472</v>
+        <v>1.578511366062685e-08</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.059487037011422e-05</v>
+        <v>5.385997496887285e-07</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0003449546056799591</v>
+        <v>1.347045213151432e-06</v>
       </c>
       <c r="CF16" t="n">
-        <v>5.619967851089314e-05</v>
+        <v>2.98797147024743e-07</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0001633759384276345</v>
+        <v>4.252068492860417e-07</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0001053683517966419</v>
+        <v>2.290759084644378e-07</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0004091931623406708</v>
+        <v>5.518448347174854e-07</v>
       </c>
       <c r="CJ16" t="n">
-        <v>7.155802450142801e-06</v>
+        <v>2.514590278224205e-07</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.0003201286599505693</v>
+        <v>2.477714815540821e-07</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.531248926767148e-05</v>
+        <v>3.204294500847027e-07</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0005792683223262429</v>
+        <v>4.32299287922433e-07</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0002798782952595502</v>
+        <v>1.442383222638455e-06</v>
       </c>
       <c r="CO16" t="n">
-        <v>8.860586603987031e-06</v>
+        <v>1.275413978873985e-06</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.000276600185316056</v>
+        <v>8.075393793660623e-07</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0005982829607091844</v>
+        <v>5.631945327877474e-07</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0002586430346127599</v>
+        <v>1.661995952417783e-06</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.000231253681704402</v>
+        <v>4.155898523094947e-07</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.0005265375948511064</v>
+        <v>2.073706468763703e-07</v>
       </c>
       <c r="CU16" t="n">
-        <v>2.880404281313531e-06</v>
+        <v>6.129679377409047e-07</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.913232128776144e-05</v>
+        <v>4.155480155532132e-07</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0002588022616691887</v>
+        <v>1.320375758950831e-06</v>
       </c>
       <c r="CX16" t="n">
-        <v>6.595728336833417e-05</v>
+        <v>2.79240367717648e-07</v>
       </c>
       <c r="CY16" t="n">
-        <v>7.24763231119141e-05</v>
+        <v>3.828866965704947e-07</v>
       </c>
       <c r="CZ16" t="n">
-        <v>7.351903332164511e-05</v>
+        <v>2.410033062005823e-07</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0005033847410231829</v>
+        <v>6.258143798731908e-07</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.000133956375066191</v>
+        <v>2.906668861157868e-08</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0001414860307704657</v>
+        <v>5.17081900852645e-07</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.361245267617051e-05</v>
+        <v>2.04627170319327e-07</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0001840058394009247</v>
+        <v>9.935797606885899e-08</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0004353065451141447</v>
+        <v>4.905209607386496e-07</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.0001124633854487911</v>
+        <v>1.351391176740435e-08</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0004309006326366216</v>
+        <v>5.5170488622025e-07</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.001441798638552427</v>
+        <v>1.52244081164099e-06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.001165788504295051</v>
+        <v>1.114158862947079e-07</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0003279514494352043</v>
+        <v>3.981136558195431e-07</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.001305360696278512</v>
+        <v>4.512535838330223e-07</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0008538728579878807</v>
+        <v>7.501382128793921e-07</v>
       </c>
       <c r="DN16" t="n">
-        <v>6.205255340319127e-05</v>
+        <v>2.338894233844258e-07</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0001897555775940418</v>
+        <v>1.078246100405522e-06</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0001811215915950015</v>
+        <v>4.255041687883931e-07</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0008919966639950871</v>
+        <v>4.195724727651395e-07</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0001851658016676083</v>
+        <v>5.693294724551379e-07</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0005607794155366719</v>
+        <v>8.631114951640484e-07</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.0001603264827281237</v>
+        <v>4.240898192620079e-07</v>
       </c>
       <c r="DU16" t="n">
-        <v>7.297884440049529e-05</v>
+        <v>8.221802545449464e-07</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.000437184004113e-05</v>
+        <v>6.402127610272146e-07</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0004421485646162182</v>
+        <v>6.060226382942346e-07</v>
       </c>
       <c r="DX16" t="n">
-        <v>2.597149432403967e-05</v>
+        <v>7.053902777443e-07</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0009215433383360505</v>
+        <v>4.827306270271947e-07</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0003854109672829509</v>
+        <v>7.385320941466489e-07</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0004294737882446498</v>
+        <v>1.174494173028506e-07</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.191794581245631e-05</v>
+        <v>5.271682539387257e-07</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.379836976411752e-05</v>
+        <v>1.208036337629892e-08</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0001178236634586938</v>
+        <v>1.23848622024525e-06</v>
       </c>
       <c r="EE16" t="n">
-        <v>5.154999234946445e-05</v>
+        <v>2.935193492703547e-07</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0002452242479193956</v>
+        <v>3.333408926664561e-07</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0004920301144011319</v>
+        <v>7.899335940919627e-08</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0002311584685230628</v>
+        <v>6.326716857074643e-07</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.0003294980269856751</v>
+        <v>3.021089867161209e-08</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0003065640630666167</v>
+        <v>3.302338313915243e-07</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0001794665440684184</v>
+        <v>3.486504738248186e-07</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0002378442150074989</v>
+        <v>1.85722335288574e-08</v>
       </c>
       <c r="EM16" t="n">
-        <v>1.003787838271819e-05</v>
+        <v>2.732172674768663e-07</v>
       </c>
       <c r="EN16" t="n">
-        <v>8.448371954727918e-05</v>
+        <v>1.314917597028398e-07</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.0001507571141701192</v>
+        <v>8.504600828018738e-07</v>
       </c>
       <c r="EP16" t="n">
-        <v>9.92420973489061e-05</v>
+        <v>4.528642421064433e-07</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0001325387274846435</v>
+        <v>5.188535396882799e-07</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0001714945246931165</v>
+        <v>2.289043266046065e-07</v>
       </c>
       <c r="ES16" t="n">
-        <v>4.84064657939598e-05</v>
+        <v>7.551869316557713e-07</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.000325822300510481</v>
+        <v>8.938706059780088e-07</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0007490671705454588</v>
+        <v>3.32215194021046e-07</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.00120644411072135</v>
+        <v>1.592889447010748e-07</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0006379781407304108</v>
+        <v>5.794186108687427e-07</v>
       </c>
       <c r="EX16" t="n">
-        <v>7.610733155161142e-05</v>
+        <v>5.538219056688831e-07</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0002150771615561098</v>
+        <v>1.460409862374945e-06</v>
       </c>
       <c r="EZ16" t="n">
-        <v>6.597601168323308e-05</v>
+        <v>1.889694090095873e-07</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0001797287259250879</v>
+        <v>3.852107965940377e-07</v>
       </c>
       <c r="FB16" t="n">
-        <v>9.124413190875202e-05</v>
+        <v>2.643546892500126e-08</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.0003199436469003558</v>
+        <v>4.468454903872043e-07</v>
       </c>
       <c r="FD16" t="n">
-        <v>9.492282697465271e-05</v>
+        <v>3.220671942472109e-07</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0001233122893609107</v>
+        <v>3.416993195060058e-07</v>
       </c>
       <c r="FF16" t="n">
-        <v>1.781335777195636e-05</v>
+        <v>6.029463861523254e-08</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0002039828104898334</v>
+        <v>6.279605457848447e-08</v>
       </c>
       <c r="FH16" t="n">
-        <v>8.497256203554571e-05</v>
+        <v>9.068396593647776e-07</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0002217336150351912</v>
+        <v>7.830155936972005e-07</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0008506809826940298</v>
+        <v>4.981985739505035e-07</v>
       </c>
       <c r="FK16" t="n">
-        <v>3.656372427940369e-05</v>
+        <v>9.182838311971864e-08</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0005196219426579773</v>
+        <v>9.437877679374651e-07</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.0002625067427288741</v>
+        <v>3.04703178244381e-07</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0004669301561079919</v>
+        <v>2.309148783297132e-07</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0008306963718496263</v>
+        <v>8.067073622441967e-07</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0003849497879855335</v>
+        <v>1.588541181263281e-06</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0003444184549152851</v>
+        <v>2.063738065771759e-06</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.001945246593095362</v>
+        <v>4.570042619889136e-07</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.000166723970323801</v>
+        <v>1.402954126206168e-06</v>
       </c>
       <c r="FT16" t="n">
-        <v>8.539843838661909e-05</v>
+        <v>5.972469239168277e-07</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0005670787650160491</v>
+        <v>1.34797642203921e-06</v>
       </c>
       <c r="FV16" t="n">
-        <v>9.932500688591972e-05</v>
+        <v>7.581489285257703e-07</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0006922588218003511</v>
+        <v>7.901981575741956e-07</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.0001935465697897598</v>
+        <v>4.719661319541046e-07</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0001105610208469443</v>
+        <v>6.148829356789065e-07</v>
       </c>
       <c r="FZ16" t="n">
-        <v>4.53572029073257e-05</v>
+        <v>7.102384813606477e-08</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0002256279985886067</v>
+        <v>6.911566288181348e-07</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.0004448812978807837</v>
+        <v>1.180144053591903e-07</v>
       </c>
       <c r="GC16" t="n">
-        <v>2.480467446730472e-05</v>
+        <v>6.199211952662154e-07</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.480011997045949e-05</v>
+        <v>9.390202535541903e-07</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0004557003558147699</v>
+        <v>8.775192554821842e-07</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0004793099651578814</v>
+        <v>2.445864311084733e-07</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.000160210402100347</v>
+        <v>6.893224622217531e-07</v>
       </c>
     </row>
     <row r="17">
@@ -10103,571 +10103,571 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.401902384008281e-05</v>
+        <v>6.554111314471811e-05</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001292182132601738</v>
+        <v>0.0001920601353049278</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001702952577034011</v>
+        <v>3.362145071150735e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004728451312985271</v>
+        <v>3.66118001693394e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0006064593326300383</v>
+        <v>2.519960253266618e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0006038479623384774</v>
+        <v>0.00012260174844414</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001039950366248377</v>
+        <v>6.909216608619317e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0004463295626919717</v>
+        <v>0.0001137792569352314</v>
       </c>
       <c r="I18" t="n">
-        <v>2.824783587129787e-05</v>
+        <v>1.607931153557729e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>2.33800892601721e-06</v>
+        <v>3.574719085008837e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001060291077010334</v>
+        <v>0.0002489550970494747</v>
       </c>
       <c r="L18" t="n">
-        <v>7.576533243991435e-05</v>
+        <v>5.079774564364925e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0002201384049840271</v>
+        <v>0.0001155947102233768</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0004065883404109627</v>
+        <v>4.723624078906141e-05</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0005684426869265735</v>
+        <v>0.0001126827628468163</v>
       </c>
       <c r="P18" t="n">
-        <v>8.606187475379556e-05</v>
+        <v>6.624722300330177e-05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.659639332909137e-05</v>
+        <v>7.586881565657677e-06</v>
       </c>
       <c r="R18" t="n">
-        <v>3.861586446873844e-05</v>
+        <v>4.16284310631454e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>2.20948950300226e-05</v>
+        <v>3.956437467422802e-06</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0001829843677114695</v>
+        <v>3.420939538045786e-05</v>
       </c>
       <c r="U18" t="n">
-        <v>2.068440335278865e-05</v>
+        <v>8.258688467321917e-06</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0001934777392307296</v>
+        <v>3.966605436289683e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0002033064956776798</v>
+        <v>2.229751771665178e-05</v>
       </c>
       <c r="X18" t="n">
-        <v>3.158739855280146e-05</v>
+        <v>8.293480277643539e-06</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.661518222652376e-05</v>
+        <v>2.110666537191719e-05</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0001776830613380298</v>
+        <v>1.263381000171648e-05</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0001040411661961116</v>
+        <v>1.178632282972103e-05</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.142297206679359e-05</v>
+        <v>2.503637006157078e-05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.000116024435556028</v>
+        <v>3.562279016477987e-05</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.171160642523319e-05</v>
+        <v>1.030327075568493e-05</v>
       </c>
       <c r="AE18" t="n">
-        <v>7.934310269774869e-05</v>
+        <v>6.128550739958882e-05</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.364289295859635e-05</v>
+        <v>5.86149180890061e-05</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.198097743326798e-05</v>
+        <v>1.601631538505899e-06</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0001350525999441743</v>
+        <v>1.891577085189056e-05</v>
       </c>
       <c r="AI18" t="n">
-        <v>9.200136264553294e-05</v>
+        <v>9.084319026442245e-05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.781326060765423e-05</v>
+        <v>1.891988540592138e-05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0001453262229915708</v>
+        <v>8.278717359644361e-06</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0002590632648207247</v>
+        <v>3.62262362614274e-05</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.043370816158131e-05</v>
+        <v>1.331987732555717e-05</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.051358210854232e-05</v>
+        <v>1.769799928297289e-05</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.858344123524148e-05</v>
+        <v>4.059991169924615e-06</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0002087113389279693</v>
+        <v>4.28778694185894e-05</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.504057192709297e-06</v>
+        <v>5.020658136345446e-05</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.0001404272043146193</v>
+        <v>7.69628313719295e-05</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.0001039271301124245</v>
+        <v>9.0344747150084e-06</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.120538844494149e-05</v>
+        <v>3.093505438300781e-05</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0009676952031441033</v>
+        <v>0.0002205178025178611</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.582851059036329e-05</v>
+        <v>2.378363387833815e-05</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.603933045174927e-05</v>
+        <v>2.874022902688012e-05</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.0001108209398807958</v>
+        <v>8.675866411067545e-05</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.0002443601551931351</v>
+        <v>0.0001240554265677929</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.854912498965859e-05</v>
+        <v>3.046605343115516e-06</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.0002873443881981075</v>
+        <v>6.512756954180077e-06</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.763920176425017e-05</v>
+        <v>2.277516068716068e-05</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.051310391630977e-05</v>
+        <v>1.639696893107612e-05</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.0001333767140749842</v>
+        <v>3.180466592311859e-06</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.0001511079026386142</v>
+        <v>1.876560236269142e-05</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.139506098814309e-05</v>
+        <v>3.775203367695212e-05</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.00039811892202124</v>
+        <v>1.079629146261141e-05</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.0001819919270928949</v>
+        <v>1.256823179573985e-05</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.0001643328578211367</v>
+        <v>4.162051482126117e-06</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.0001541830861242488</v>
+        <v>6.027604467817582e-05</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.116206400794908e-05</v>
+        <v>1.279569733014796e-05</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.0001634694781387225</v>
+        <v>6.28249290457461e-06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.0002378343779128045</v>
+        <v>6.307013973128051e-05</v>
       </c>
       <c r="BN18" t="n">
-        <v>7.044597441563383e-05</v>
+        <v>2.5896666556946e-05</v>
       </c>
       <c r="BO18" t="n">
-        <v>6.079109880374745e-05</v>
+        <v>3.05955018120585e-06</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.490727249300107e-05</v>
+        <v>4.328059731051326e-05</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.0001171592812170275</v>
+        <v>1.607380909263156e-05</v>
       </c>
       <c r="BR18" t="n">
-        <v>4.89417725475505e-05</v>
+        <v>7.245424785651267e-05</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.244066364364699e-05</v>
+        <v>5.935093213338405e-06</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.0001131908647948876</v>
+        <v>2.178129216190428e-05</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.695176413515583e-05</v>
+        <v>2.675938958418556e-06</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0005903651472181082</v>
+        <v>0.0001279444841202348</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.0002287314127897844</v>
+        <v>1.54561876115622e-05</v>
       </c>
       <c r="BX18" t="n">
-        <v>2.741377102211118e-05</v>
+        <v>7.807258953107521e-06</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.807668200461194e-05</v>
+        <v>2.399564982624725e-05</v>
       </c>
       <c r="BZ18" t="n">
-        <v>9.682691597845405e-06</v>
+        <v>4.69128972326871e-05</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.714732156367972e-05</v>
+        <v>4.19587959186174e-05</v>
       </c>
       <c r="CB18" t="n">
-        <v>8.63572204252705e-05</v>
+        <v>9.192533980240114e-06</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.779983282787725e-05</v>
+        <v>1.066264485416468e-05</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.267898162244819e-05</v>
+        <v>9.707378012535628e-07</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.0001908259000629187</v>
+        <v>6.285166455199942e-05</v>
       </c>
       <c r="CF18" t="n">
-        <v>5.406359196058474e-05</v>
+        <v>3.635739631135948e-06</v>
       </c>
       <c r="CG18" t="n">
-        <v>9.124888310907409e-05</v>
+        <v>3.756202659133123e-06</v>
       </c>
       <c r="CH18" t="n">
-        <v>2.819038127199747e-05</v>
+        <v>1.102185342460871e-05</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.0001025857636705041</v>
+        <v>2.599407162051648e-05</v>
       </c>
       <c r="CJ18" t="n">
-        <v>8.658706065034494e-05</v>
+        <v>5.060598596173804e-06</v>
       </c>
       <c r="CK18" t="n">
-        <v>9.126461372943595e-05</v>
+        <v>1.300197800446767e-05</v>
       </c>
       <c r="CL18" t="n">
-        <v>5.516297096619383e-05</v>
+        <v>6.821684337410261e-07</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.0001486252440372482</v>
+        <v>6.595419836230576e-05</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.0001030690764309838</v>
+        <v>0.0001204444415634498</v>
       </c>
       <c r="CO18" t="n">
-        <v>8.997063559945673e-06</v>
+        <v>2.588566712802276e-05</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.0001491573348175734</v>
+        <v>5.148883064975962e-05</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0001882305659819394</v>
+        <v>4.696770702139474e-05</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.0001346874487353489</v>
+        <v>3.011909029737581e-05</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.0002324900269741192</v>
+        <v>7.672591891605407e-06</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.0001643505675019696</v>
+        <v>3.67536922567524e-05</v>
       </c>
       <c r="CU18" t="n">
-        <v>6.036903141648509e-05</v>
+        <v>2.015792233578395e-05</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.96670405077748e-05</v>
+        <v>1.276711373066064e-05</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.0001674085797276348</v>
+        <v>6.271777237998322e-05</v>
       </c>
       <c r="CX18" t="n">
-        <v>7.137400098145008e-05</v>
+        <v>1.243395490746479e-05</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.0001383216003887355</v>
+        <v>1.302598775509978e-05</v>
       </c>
       <c r="CZ18" t="n">
-        <v>1.770955350366421e-05</v>
+        <v>5.745519501942908e-06</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.0001662572467466816</v>
+        <v>2.749663690337911e-05</v>
       </c>
       <c r="DB18" t="n">
-        <v>7.283958257175982e-05</v>
+        <v>7.080044269969221e-06</v>
       </c>
       <c r="DC18" t="n">
-        <v>0.0001127259893110022</v>
+        <v>8.865785275702365e-06</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.822271951823495e-05</v>
+        <v>3.283088062744355e-06</v>
       </c>
       <c r="DE18" t="n">
-        <v>4.797969450009987e-05</v>
+        <v>5.184059318708023e-06</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.0001265328755835071</v>
+        <v>5.960814087302424e-05</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.386381260701455e-05</v>
+        <v>2.979380769829731e-05</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.0004951834562234581</v>
+        <v>5.588838757830672e-05</v>
       </c>
       <c r="DI18" t="n">
-        <v>9.46257496252656e-05</v>
+        <v>6.334306817734614e-06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>7.512947195209563e-05</v>
+        <v>5.571135625359602e-05</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.0001642851275391877</v>
+        <v>1.3605574167741e-05</v>
       </c>
       <c r="DL18" t="n">
-        <v>9.402209980180487e-05</v>
+        <v>8.783923476585187e-06</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.0001270927459700033</v>
+        <v>3.30934017256368e-06</v>
       </c>
       <c r="DN18" t="n">
-        <v>5.229611997492611e-05</v>
+        <v>5.188845534576103e-05</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.0001047901387210004</v>
+        <v>3.879420910379849e-05</v>
       </c>
       <c r="DP18" t="n">
-        <v>5.366470577428117e-05</v>
+        <v>1.873489600257017e-05</v>
       </c>
       <c r="DQ18" t="n">
-        <v>5.363857781048864e-06</v>
+        <v>5.749056435888633e-05</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.053507655044086e-05</v>
+        <v>1.055091706803069e-05</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.0001817310258047655</v>
+        <v>1.735028490656987e-06</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.0001189072427223437</v>
+        <v>7.62659874453675e-06</v>
       </c>
       <c r="DU18" t="n">
-        <v>2.385421430517454e-05</v>
+        <v>2.48313881456852e-06</v>
       </c>
       <c r="DV18" t="n">
-        <v>4.30831678386312e-05</v>
+        <v>4.841992267756723e-05</v>
       </c>
       <c r="DW18" t="n">
-        <v>6.169421249069273e-05</v>
+        <v>4.470246494747698e-05</v>
       </c>
       <c r="DX18" t="n">
-        <v>5.036174115957692e-05</v>
+        <v>4.335688572609797e-05</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.0001706808543531224</v>
+        <v>1.066772892954759e-05</v>
       </c>
       <c r="DZ18" t="n">
-        <v>1.192283889395185e-05</v>
+        <v>3.597597697080346e-06</v>
       </c>
       <c r="EA18" t="n">
-        <v>5.78511826461181e-05</v>
+        <v>3.300203752587549e-05</v>
       </c>
       <c r="EB18" t="n">
-        <v>8.963925938587636e-05</v>
+        <v>1.056977271218784e-05</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.277738192584366e-06</v>
+        <v>6.639844741584966e-06</v>
       </c>
       <c r="ED18" t="n">
-        <v>2.095452873618342e-05</v>
+        <v>2.815600964822806e-05</v>
       </c>
       <c r="EE18" t="n">
-        <v>6.058268263586797e-05</v>
+        <v>4.383995474199764e-05</v>
       </c>
       <c r="EF18" t="n">
-        <v>7.117410132195801e-05</v>
+        <v>3.555084731488023e-06</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.0001905192766571417</v>
+        <v>1.985669587156735e-05</v>
       </c>
       <c r="EH18" t="n">
-        <v>8.764947415329516e-05</v>
+        <v>3.003241545229685e-06</v>
       </c>
       <c r="EI18" t="n">
-        <v>2.79797641269397e-05</v>
+        <v>4.638328027795069e-05</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.0001748501672409475</v>
+        <v>4.077887933817692e-05</v>
       </c>
       <c r="EK18" t="n">
-        <v>6.538575689774007e-05</v>
+        <v>1.744863584463019e-05</v>
       </c>
       <c r="EL18" t="n">
-        <v>8.549439371563494e-05</v>
+        <v>8.648163202451542e-06</v>
       </c>
       <c r="EM18" t="n">
-        <v>4.36566406278871e-05</v>
+        <v>1.153675202658633e-05</v>
       </c>
       <c r="EN18" t="n">
-        <v>3.506553184706718e-06</v>
+        <v>3.878550160152372e-06</v>
       </c>
       <c r="EO18" t="n">
-        <v>1.20778895507101e-06</v>
+        <v>1.347391298622824e-05</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.0001031684805639088</v>
+        <v>1.644831718294881e-05</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0.0001265140308532864</v>
+        <v>9.162249625660479e-06</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.0001404064532835037</v>
+        <v>1.919214810186531e-05</v>
       </c>
       <c r="ES18" t="n">
-        <v>7.164194539655e-05</v>
+        <v>1.949779652932193e-05</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.0001752158277668059</v>
+        <v>2.4825027139741e-05</v>
       </c>
       <c r="EU18" t="n">
-        <v>6.97245413903147e-05</v>
+        <v>2.37345147979795e-07</v>
       </c>
       <c r="EV18" t="n">
-        <v>0.0002414837945252657</v>
+        <v>1.592550870554987e-05</v>
       </c>
       <c r="EW18" t="n">
-        <v>4.607180380844511e-05</v>
+        <v>3.191340738339932e-06</v>
       </c>
       <c r="EX18" t="n">
-        <v>1.760348459356464e-05</v>
+        <v>6.240734364837408e-06</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.0001485464163124561</v>
+        <v>6.929481605766341e-05</v>
       </c>
       <c r="EZ18" t="n">
-        <v>4.204396100249141e-05</v>
+        <v>1.547432475490496e-06</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.0001104671246139333</v>
+        <v>5.397022960096365e-06</v>
       </c>
       <c r="FB18" t="n">
-        <v>1.491816647103406e-06</v>
+        <v>2.900640083680628e-06</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.0001160175088443793</v>
+        <v>2.353158379264642e-05</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.0001090904988814145</v>
+        <v>6.56748443361721e-06</v>
       </c>
       <c r="FE18" t="n">
-        <v>9.569751273375005e-05</v>
+        <v>7.942014235595707e-06</v>
       </c>
       <c r="FF18" t="n">
-        <v>5.97088728682138e-05</v>
+        <v>6.660681719949935e-06</v>
       </c>
       <c r="FG18" t="n">
-        <v>4.436466406332329e-05</v>
+        <v>9.481746019446291e-06</v>
       </c>
       <c r="FH18" t="n">
-        <v>6.898602441651747e-05</v>
+        <v>3.352186831762083e-05</v>
       </c>
       <c r="FI18" t="n">
-        <v>0.0001606604200787842</v>
+        <v>2.525224408600479e-05</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.0002200083545176312</v>
+        <v>3.579580152290873e-05</v>
       </c>
       <c r="FK18" t="n">
-        <v>4.03248704969883e-05</v>
+        <v>2.895179386541713e-05</v>
       </c>
       <c r="FL18" t="n">
-        <v>2.177744318032637e-05</v>
+        <v>4.929523129248992e-05</v>
       </c>
       <c r="FM18" t="n">
-        <v>1.951966623892076e-05</v>
+        <v>2.240930371044669e-05</v>
       </c>
       <c r="FN18" t="n">
-        <v>9.476990817347541e-05</v>
+        <v>3.043935066671111e-05</v>
       </c>
       <c r="FO18" t="n">
-        <v>0.0001026115933200344</v>
+        <v>7.809924136381596e-05</v>
       </c>
       <c r="FP18" t="n">
-        <v>4.358415026217699e-05</v>
+        <v>2.976557880174369e-05</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.0002382879029028118</v>
+        <v>5.893517663935199e-05</v>
       </c>
       <c r="FR18" t="n">
-        <v>0.0001105892879422754</v>
+        <v>6.153751019155607e-05</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.0001777086581569165</v>
+        <v>4.719410208053887e-05</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.0001700008288025856</v>
+        <v>4.849977631238289e-05</v>
       </c>
       <c r="FU18" t="n">
-        <v>9.991059414460324e-06</v>
+        <v>1.101786983781494e-05</v>
       </c>
       <c r="FV18" t="n">
-        <v>9.985364158637822e-05</v>
+        <v>3.15198085445445e-05</v>
       </c>
       <c r="FW18" t="n">
-        <v>3.304829078842886e-06</v>
+        <v>4.998711301595904e-05</v>
       </c>
       <c r="FX18" t="n">
-        <v>4.197063390165567e-05</v>
+        <v>5.697225788026117e-05</v>
       </c>
       <c r="FY18" t="n">
-        <v>0.0001631668274058029</v>
+        <v>1.051470280799549e-05</v>
       </c>
       <c r="FZ18" t="n">
-        <v>5.311920176609419e-05</v>
+        <v>1.826485458877869e-05</v>
       </c>
       <c r="GA18" t="n">
-        <v>4.177528171567246e-05</v>
+        <v>5.639123264700174e-05</v>
       </c>
       <c r="GB18" t="n">
-        <v>8.274841820821166e-05</v>
+        <v>9.267494533560239e-06</v>
       </c>
       <c r="GC18" t="n">
-        <v>5.152887024451047e-05</v>
+        <v>5.870580935152248e-05</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.0001364487980026752</v>
+        <v>4.649415132007562e-06</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.0004123153048567474</v>
+        <v>5.046306250733323e-05</v>
       </c>
       <c r="GF18" t="n">
-        <v>6.681570084765553e-06</v>
+        <v>1.528735265310388e-05</v>
       </c>
       <c r="GG18" t="n">
-        <v>5.037586743128486e-05</v>
+        <v>9.988254532800056e-06</v>
       </c>
     </row>
   </sheetData>
